--- a/collected-data.xlsx
+++ b/collected-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-26.04\home\leo\OS-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682C65F3-245D-4FCF-82EE-4C36044D5133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E070EF-40DA-4B39-9A41-2F7BC3042639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4356" yWindow="1884" windowWidth="26784" windowHeight="16032" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="528" windowWidth="26784" windowHeight="16032" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1357,9 +1357,6 @@
     <t>可访问；以 GitHub 完整镜像为准</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/T202510486995205-1539</t>
-  </si>
-  <si>
     <t>RuOK</t>
   </si>
   <si>
@@ -2866,6 +2863,10 @@
   </si>
   <si>
     <t>https://gitlab.eduxiji.net/T202510558995240/oskernel2025-konosuba</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/T202510486995205-1539</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7696,8 +7697,8 @@
       <c r="I122" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="J122" s="3" t="s">
-        <v>445</v>
+      <c r="J122" s="1" t="s">
+        <v>941</v>
       </c>
       <c r="K122" s="3" t="s">
         <v>19</v>
@@ -7720,20 +7721,20 @@
         <v>430</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H123" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="I123" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="K123" s="3" t="s">
         <v>19</v>
@@ -7756,20 +7757,20 @@
         <v>430</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H124" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J124" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="K124" s="3" t="s">
         <v>19</v>
@@ -7792,20 +7793,20 @@
         <v>430</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K125" s="3" t="s">
         <v>19</v>
@@ -7828,20 +7829,20 @@
         <v>430</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>19</v>
@@ -7864,7 +7865,7 @@
         <v>430</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
@@ -7875,7 +7876,7 @@
         <v>17</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>19</v>
@@ -7898,20 +7899,20 @@
         <v>430</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K128" s="3" t="s">
         <v>19</v>
@@ -7934,20 +7935,20 @@
         <v>430</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>19</v>
@@ -7967,25 +7968,25 @@
         <v>14</v>
       </c>
       <c r="D130" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="F130" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="G130" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="G130" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H130" s="3" t="s">
+      <c r="I130" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J130" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="I130" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="K130" s="3" t="s">
         <v>19</v>
@@ -8005,23 +8006,23 @@
         <v>14</v>
       </c>
       <c r="D131" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E131" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H131" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J131" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="I131" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J131" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="K131" s="3" t="s">
         <v>19</v>
@@ -8041,17 +8042,17 @@
         <v>14</v>
       </c>
       <c r="D132" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>19</v>
@@ -8075,23 +8076,23 @@
         <v>75</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K133" s="3" t="s">
         <v>19</v>
@@ -8111,25 +8112,25 @@
         <v>14</v>
       </c>
       <c r="D134" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="E134" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="F134" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="G134" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H134" s="3" t="s">
+      <c r="I134" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J134" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="I134" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="K134" s="3" t="s">
         <v>19</v>
@@ -8149,17 +8150,17 @@
         <v>14</v>
       </c>
       <c r="D135" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>19</v>
@@ -8183,25 +8184,25 @@
         <v>14</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E136" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="F136" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="G136" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="G136" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H136" s="3" t="s">
+      <c r="I136" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J136" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="I136" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J136" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="K136" s="3" t="s">
         <v>19</v>
@@ -8221,17 +8222,17 @@
         <v>14</v>
       </c>
       <c r="D137" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E137" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>19</v>
@@ -8255,25 +8256,25 @@
         <v>14</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E138" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="F138" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="G138" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="G138" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H138" s="3" t="s">
+      <c r="I138" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J138" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J138" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="K138" s="3" t="s">
         <v>19</v>
@@ -8293,17 +8294,17 @@
         <v>14</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>19</v>
@@ -8327,25 +8328,25 @@
         <v>14</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E140" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="F140" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="G140" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="G140" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H140" s="3" t="s">
+      <c r="I140" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J140" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="I140" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J140" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>19</v>
@@ -8365,25 +8366,25 @@
         <v>14</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E141" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="F141" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="G141" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H141" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H141" s="3" t="s">
+      <c r="I141" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J141" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="I141" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J141" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="K141" s="3" t="s">
         <v>19</v>
@@ -8403,23 +8404,23 @@
         <v>14</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H142" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J142" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="I142" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J142" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>19</v>
@@ -8439,10 +8440,10 @@
         <v>14</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
@@ -8453,7 +8454,7 @@
         <v>17</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K143" s="3" t="s">
         <v>19</v>
@@ -8473,23 +8474,23 @@
         <v>75</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K144" s="3" t="s">
         <v>19</v>
@@ -8509,10 +8510,10 @@
         <v>75</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -8523,7 +8524,7 @@
         <v>17</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K145" s="3" t="s">
         <v>19</v>
@@ -8543,23 +8544,23 @@
         <v>75</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K146" s="3" t="s">
         <v>19</v>
@@ -8579,23 +8580,23 @@
         <v>75</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K147" s="3" t="s">
         <v>19</v>
@@ -8615,23 +8616,23 @@
         <v>75</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K148" s="3" t="s">
         <v>19</v>
@@ -8651,23 +8652,23 @@
         <v>14</v>
       </c>
       <c r="D149" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E149" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>529</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H149" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J149" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="I149" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J149" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>19</v>
@@ -8687,13 +8688,13 @@
         <v>14</v>
       </c>
       <c r="D150" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E150" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="E150" s="3" t="s">
+      <c r="F150" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>19</v>
@@ -8703,7 +8704,7 @@
         <v>17</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>19</v>
@@ -8723,25 +8724,25 @@
         <v>14</v>
       </c>
       <c r="D151" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E151" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="E151" s="3" t="s">
+      <c r="F151" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="G151" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H151" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="G151" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H151" s="3" t="s">
+      <c r="I151" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J151" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="I151" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J151" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="K151" s="3" t="s">
         <v>19</v>
@@ -8761,25 +8762,25 @@
         <v>14</v>
       </c>
       <c r="D152" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="E152" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="F152" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="F152" s="3" t="s">
+      <c r="G152" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H152" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H152" s="3" t="s">
+      <c r="I152" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J152" s="3" t="s">
         <v>544</v>
-      </c>
-      <c r="I152" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J152" s="3" t="s">
-        <v>545</v>
       </c>
       <c r="K152" s="3" t="s">
         <v>19</v>
@@ -8799,23 +8800,23 @@
         <v>14</v>
       </c>
       <c r="D153" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="E153" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H153" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J153" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="I153" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J153" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>19</v>
@@ -8835,17 +8836,17 @@
         <v>14</v>
       </c>
       <c r="D154" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E154" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>19</v>
@@ -8869,17 +8870,17 @@
         <v>14</v>
       </c>
       <c r="D155" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E155" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>554</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>19</v>
@@ -8903,25 +8904,25 @@
         <v>14</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E156" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F156" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="F156" s="3" t="s">
+      <c r="G156" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>140</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>19</v>
@@ -8941,17 +8942,17 @@
         <v>14</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>19</v>
@@ -8975,17 +8976,17 @@
         <v>14</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>19</v>
@@ -9009,25 +9010,25 @@
         <v>14</v>
       </c>
       <c r="D159" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E159" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="F159" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="G159" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H159" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H159" s="3" t="s">
+      <c r="I159" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J159" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="I159" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J159" s="3" t="s">
-        <v>568</v>
       </c>
       <c r="K159" s="3" t="s">
         <v>19</v>
@@ -9047,17 +9048,17 @@
         <v>14</v>
       </c>
       <c r="D160" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E160" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>64</v>
@@ -9081,25 +9082,25 @@
         <v>14</v>
       </c>
       <c r="D161" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E161" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="F161" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="G161" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H161" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="G161" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H161" s="3" t="s">
+      <c r="I161" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J161" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="I161" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J161" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="K161" s="3" t="s">
         <v>19</v>
@@ -9119,17 +9120,17 @@
         <v>14</v>
       </c>
       <c r="D162" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E162" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>578</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>19</v>
@@ -9153,23 +9154,23 @@
         <v>14</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K163" s="3" t="s">
         <v>19</v>
@@ -9189,23 +9190,23 @@
         <v>14</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H164" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J164" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="I164" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J164" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="K164" s="3" t="s">
         <v>19</v>
@@ -9225,17 +9226,17 @@
         <v>14</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>19</v>
@@ -9259,23 +9260,23 @@
         <v>75</v>
       </c>
       <c r="D166" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="E166" s="3" t="s">
         <v>587</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>79</v>
       </c>
       <c r="J166" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>19</v>
@@ -9295,17 +9296,17 @@
         <v>14</v>
       </c>
       <c r="D167" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E167" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>64</v>
@@ -9329,17 +9330,17 @@
         <v>14</v>
       </c>
       <c r="D168" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="E168" s="3" t="s">
         <v>594</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>595</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>19</v>
@@ -9366,10 +9367,10 @@
         <v>81</v>
       </c>
       <c r="E169" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="F169" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>598</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>19</v>
@@ -9397,13 +9398,13 @@
         <v>14</v>
       </c>
       <c r="D170" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E170" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="E170" s="3" t="s">
+      <c r="F170" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>19</v>
@@ -9434,10 +9435,10 @@
         <v>250</v>
       </c>
       <c r="E171" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F171" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>603</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>19</v>
@@ -9465,13 +9466,13 @@
         <v>14</v>
       </c>
       <c r="D172" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="E172" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="E172" s="3" t="s">
+      <c r="F172" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>19</v>
@@ -9502,10 +9503,10 @@
         <v>264</v>
       </c>
       <c r="E173" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="F173" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>19</v>
@@ -9533,13 +9534,13 @@
         <v>14</v>
       </c>
       <c r="D174" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E174" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="E174" s="3" t="s">
+      <c r="F174" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>19</v>
@@ -9567,13 +9568,13 @@
         <v>14</v>
       </c>
       <c r="D175" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E175" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="E175" s="3" t="s">
+      <c r="F175" s="3" t="s">
         <v>613</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>19</v>
@@ -9604,10 +9605,10 @@
         <v>410</v>
       </c>
       <c r="E176" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="F176" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="F176" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>19</v>
@@ -9638,10 +9639,10 @@
         <v>410</v>
       </c>
       <c r="E177" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="F177" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>618</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>19</v>
@@ -9672,10 +9673,10 @@
         <v>410</v>
       </c>
       <c r="E178" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="F178" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>620</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>19</v>
@@ -9703,13 +9704,13 @@
         <v>14</v>
       </c>
       <c r="D179" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E179" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="E179" s="3" t="s">
+      <c r="F179" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>623</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>19</v>
@@ -9737,13 +9738,13 @@
         <v>14</v>
       </c>
       <c r="D180" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="F180" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>625</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>19</v>
@@ -9771,13 +9772,13 @@
         <v>14</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E181" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="F181" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>19</v>
@@ -9805,13 +9806,13 @@
         <v>14</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E182" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="F182" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>629</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>19</v>
@@ -9839,13 +9840,13 @@
         <v>14</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E183" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="F183" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>631</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>19</v>
@@ -9873,13 +9874,13 @@
         <v>14</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E184" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="F184" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>633</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>19</v>
@@ -9910,16 +9911,16 @@
         <v>201</v>
       </c>
       <c r="E185" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="F185" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="F185" s="3" t="s">
+      <c r="G185" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H185" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>636</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>19</v>
@@ -9946,16 +9947,16 @@
         <v>43</v>
       </c>
       <c r="E186" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="F186" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="G186" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H186" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H186" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>19</v>
@@ -9982,16 +9983,16 @@
         <v>264</v>
       </c>
       <c r="E187" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="F187" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="F187" s="3" t="s">
+      <c r="G187" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H187" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H187" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>19</v>
@@ -10015,13 +10016,13 @@
         <v>14</v>
       </c>
       <c r="D188" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="E188" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="E188" s="3" t="s">
+      <c r="F188" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>645</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>19</v>
@@ -10052,16 +10053,16 @@
         <v>201</v>
       </c>
       <c r="E189" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F189" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="F189" s="3" t="s">
+      <c r="G189" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H189" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H189" s="3" t="s">
-        <v>648</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>19</v>
@@ -10085,19 +10086,19 @@
         <v>14</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E190" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="F190" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="F190" s="3" t="s">
+      <c r="G190" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H190" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H190" s="3" t="s">
-        <v>651</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>19</v>
@@ -10121,19 +10122,19 @@
         <v>14</v>
       </c>
       <c r="D191" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="E191" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="E191" s="3" t="s">
+      <c r="F191" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="F191" s="3" t="s">
+      <c r="G191" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H191" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H191" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>19</v>
@@ -10160,16 +10161,16 @@
         <v>102</v>
       </c>
       <c r="E192" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="F192" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="F192" s="3" t="s">
+      <c r="G192" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H192" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H192" s="3" t="s">
-        <v>658</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>19</v>
@@ -10193,19 +10194,19 @@
         <v>14</v>
       </c>
       <c r="D193" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="E193" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="E193" s="3" t="s">
+      <c r="F193" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="F193" s="3" t="s">
+      <c r="G193" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H193" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H193" s="3" t="s">
-        <v>662</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>19</v>
@@ -10232,16 +10233,16 @@
         <v>175</v>
       </c>
       <c r="E194" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="F194" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="F194" s="3" t="s">
+      <c r="G194" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H194" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H194" s="3" t="s">
-        <v>665</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>19</v>
@@ -10268,16 +10269,16 @@
         <v>61</v>
       </c>
       <c r="E195" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="F195" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="F195" s="3" t="s">
+      <c r="G195" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H195" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>19</v>
@@ -10304,16 +10305,16 @@
         <v>25</v>
       </c>
       <c r="E196" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F196" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="F196" s="3" t="s">
+      <c r="G196" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H196" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>671</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>19</v>
@@ -10340,16 +10341,16 @@
         <v>259</v>
       </c>
       <c r="E197" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="F197" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="F197" s="3" t="s">
+      <c r="G197" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H197" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H197" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>19</v>
@@ -10376,16 +10377,16 @@
         <v>81</v>
       </c>
       <c r="E198" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="F198" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="F198" s="3" t="s">
+      <c r="G198" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H198" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="G198" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H198" s="3" t="s">
-        <v>677</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>19</v>
@@ -10409,19 +10410,19 @@
         <v>14</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E199" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F199" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="F199" s="3" t="s">
+      <c r="G199" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H199" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>680</v>
       </c>
       <c r="I199" s="3" t="s">
         <v>19</v>
@@ -10448,16 +10449,16 @@
         <v>25</v>
       </c>
       <c r="E200" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="F200" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="F200" s="3" t="s">
+      <c r="G200" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H200" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H200" s="3" t="s">
-        <v>683</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>19</v>
@@ -10481,19 +10482,19 @@
         <v>14</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E201" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="F201" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="F201" s="3" t="s">
+      <c r="G201" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H201" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H201" s="3" t="s">
-        <v>686</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>19</v>
@@ -10520,16 +10521,16 @@
         <v>201</v>
       </c>
       <c r="E202" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="F202" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="F202" s="3" t="s">
+      <c r="G202" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H202" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H202" s="3" t="s">
-        <v>689</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>19</v>
@@ -10544,7 +10545,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B203" t="s">
         <v>13</v>
@@ -10556,10 +10557,10 @@
         <v>15</v>
       </c>
       <c r="E203" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="F203" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>692</v>
       </c>
       <c r="G203" t="s">
         <v>19</v>
@@ -10576,7 +10577,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B204" t="s">
         <v>13</v>
@@ -10589,7 +10590,7 @@
       </c>
       <c r="E204"/>
       <c r="F204" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G204" t="s">
         <v>19</v>
@@ -10606,7 +10607,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B205" t="s">
         <v>13</v>
@@ -10618,10 +10619,10 @@
         <v>25</v>
       </c>
       <c r="E205" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F205" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="G205" t="s">
         <v>19</v>
@@ -10638,7 +10639,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B206" t="s">
         <v>13</v>
@@ -10650,10 +10651,10 @@
         <v>25</v>
       </c>
       <c r="E206" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="F206" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>697</v>
       </c>
       <c r="G206" t="s">
         <v>19</v>
@@ -10670,7 +10671,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B207" t="s">
         <v>13</v>
@@ -10682,10 +10683,10 @@
         <v>25</v>
       </c>
       <c r="E207" t="s">
+        <v>697</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="G207" t="s">
         <v>19</v>
@@ -10702,7 +10703,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B208" t="s">
         <v>13</v>
@@ -10714,10 +10715,10 @@
         <v>25</v>
       </c>
       <c r="E208" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="G208" t="s">
         <v>19</v>
@@ -10734,7 +10735,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B209" t="s">
         <v>13</v>
@@ -10746,10 +10747,10 @@
         <v>25</v>
       </c>
       <c r="E209" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>703</v>
       </c>
       <c r="G209" t="s">
         <v>19</v>
@@ -10766,7 +10767,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B210" t="s">
         <v>13</v>
@@ -10779,7 +10780,7 @@
       </c>
       <c r="E210"/>
       <c r="F210" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G210" t="s">
         <v>19</v>
@@ -10796,7 +10797,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B211" t="s">
         <v>13</v>
@@ -10808,10 +10809,10 @@
         <v>25</v>
       </c>
       <c r="E211" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>705</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>706</v>
       </c>
       <c r="G211" t="s">
         <v>19</v>
@@ -10828,7 +10829,7 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B212" t="s">
         <v>13</v>
@@ -10840,10 +10841,10 @@
         <v>25</v>
       </c>
       <c r="E212" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="F212" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="G212" t="s">
         <v>19</v>
@@ -10860,7 +10861,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B213" t="s">
         <v>13</v>
@@ -10872,10 +10873,10 @@
         <v>25</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G213" t="s">
         <v>19</v>
@@ -10892,7 +10893,7 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B214" t="s">
         <v>13</v>
@@ -10905,7 +10906,7 @@
       </c>
       <c r="E214"/>
       <c r="F214" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G214" t="s">
         <v>19</v>
@@ -10922,7 +10923,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B215" t="s">
         <v>13</v>
@@ -10934,10 +10935,10 @@
         <v>61</v>
       </c>
       <c r="E215" t="s">
+        <v>710</v>
+      </c>
+      <c r="F215" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="G215" t="s">
         <v>19</v>
@@ -10954,7 +10955,7 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B216" t="s">
         <v>13</v>
@@ -10966,10 +10967,10 @@
         <v>61</v>
       </c>
       <c r="E216" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="F216" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="F216" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="G216" t="s">
         <v>19</v>
@@ -10986,7 +10987,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B217" t="s">
         <v>13</v>
@@ -10999,7 +11000,7 @@
       </c>
       <c r="E217"/>
       <c r="F217" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G217" t="s">
         <v>19</v>
@@ -11016,7 +11017,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B218" t="s">
         <v>13</v>
@@ -11028,10 +11029,10 @@
         <v>43</v>
       </c>
       <c r="E218" t="s">
+        <v>715</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>717</v>
       </c>
       <c r="G218" t="s">
         <v>19</v>
@@ -11048,7 +11049,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B219" t="s">
         <v>13</v>
@@ -11060,10 +11061,10 @@
         <v>43</v>
       </c>
       <c r="E219" t="s">
+        <v>717</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>718</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>719</v>
       </c>
       <c r="G219" t="s">
         <v>19</v>
@@ -11080,7 +11081,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B220" t="s">
         <v>13</v>
@@ -11089,13 +11090,13 @@
         <v>14</v>
       </c>
       <c r="D220" t="s">
+        <v>719</v>
+      </c>
+      <c r="E220" t="s">
         <v>720</v>
       </c>
-      <c r="E220" t="s">
+      <c r="F220" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>722</v>
       </c>
       <c r="G220" t="s">
         <v>19</v>
@@ -11112,7 +11113,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B221" t="s">
         <v>13</v>
@@ -11121,13 +11122,13 @@
         <v>14</v>
       </c>
       <c r="D221" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E221" t="s">
+        <v>722</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="G221" t="s">
         <v>19</v>
@@ -11144,7 +11145,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B222" t="s">
         <v>13</v>
@@ -11156,10 +11157,10 @@
         <v>336</v>
       </c>
       <c r="E222" t="s">
+        <v>724</v>
+      </c>
+      <c r="F222" t="s">
         <v>725</v>
-      </c>
-      <c r="F222" t="s">
-        <v>726</v>
       </c>
       <c r="G222" t="s">
         <v>19</v>
@@ -11176,7 +11177,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B223" t="s">
         <v>13</v>
@@ -11188,10 +11189,10 @@
         <v>336</v>
       </c>
       <c r="E223" t="s">
+        <v>726</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>727</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>728</v>
       </c>
       <c r="G223" t="s">
         <v>19</v>
@@ -11208,7 +11209,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B224" t="s">
         <v>13</v>
@@ -11220,10 +11221,10 @@
         <v>405</v>
       </c>
       <c r="E224" t="s">
+        <v>728</v>
+      </c>
+      <c r="F224" s="1" t="s">
         <v>729</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="G224" t="s">
         <v>19</v>
@@ -11240,7 +11241,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B225" t="s">
         <v>13</v>
@@ -11249,13 +11250,13 @@
         <v>14</v>
       </c>
       <c r="D225" t="s">
+        <v>730</v>
+      </c>
+      <c r="E225" t="s">
         <v>731</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" s="1" t="s">
         <v>732</v>
-      </c>
-      <c r="F225" s="1" t="s">
-        <v>733</v>
       </c>
       <c r="G225" t="s">
         <v>19</v>
@@ -11272,7 +11273,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B226" t="s">
         <v>13</v>
@@ -11281,13 +11282,13 @@
         <v>14</v>
       </c>
       <c r="D226" t="s">
+        <v>733</v>
+      </c>
+      <c r="E226" t="s">
         <v>734</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="F226" s="1" t="s">
-        <v>736</v>
       </c>
       <c r="G226" t="s">
         <v>19</v>
@@ -11304,7 +11305,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B227" t="s">
         <v>13</v>
@@ -11313,13 +11314,13 @@
         <v>14</v>
       </c>
       <c r="D227" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E227" t="s">
+        <v>736</v>
+      </c>
+      <c r="F227" s="1" t="s">
         <v>737</v>
-      </c>
-      <c r="F227" s="1" t="s">
-        <v>738</v>
       </c>
       <c r="G227" t="s">
         <v>19</v>
@@ -11336,7 +11337,7 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B228" t="s">
         <v>13</v>
@@ -11348,10 +11349,10 @@
         <v>354</v>
       </c>
       <c r="E228" t="s">
+        <v>738</v>
+      </c>
+      <c r="F228" s="1" t="s">
         <v>739</v>
-      </c>
-      <c r="F228" s="1" t="s">
-        <v>740</v>
       </c>
       <c r="G228" t="s">
         <v>19</v>
@@ -11368,7 +11369,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B229" t="s">
         <v>13</v>
@@ -11380,10 +11381,10 @@
         <v>354</v>
       </c>
       <c r="E229" t="s">
+        <v>740</v>
+      </c>
+      <c r="F229" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="F229" s="1" t="s">
-        <v>742</v>
       </c>
       <c r="G229" t="s">
         <v>19</v>
@@ -11400,7 +11401,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B230" t="s">
         <v>13</v>
@@ -11413,7 +11414,7 @@
       </c>
       <c r="E230"/>
       <c r="F230" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G230" t="s">
         <v>19</v>
@@ -11430,7 +11431,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B231" t="s">
         <v>13</v>
@@ -11443,7 +11444,7 @@
       </c>
       <c r="E231"/>
       <c r="F231" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G231" t="s">
         <v>19</v>
@@ -11460,7 +11461,7 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B232" t="s">
         <v>13</v>
@@ -11472,10 +11473,10 @@
         <v>306</v>
       </c>
       <c r="E232" t="s">
+        <v>744</v>
+      </c>
+      <c r="F232" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="F232" s="1" t="s">
-        <v>746</v>
       </c>
       <c r="G232" t="s">
         <v>19</v>
@@ -11492,7 +11493,7 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B233" t="s">
         <v>13</v>
@@ -11505,7 +11506,7 @@
       </c>
       <c r="E233"/>
       <c r="F233" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G233" t="s">
         <v>19</v>
@@ -11522,7 +11523,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B234" t="s">
         <v>13</v>
@@ -11535,7 +11536,7 @@
       </c>
       <c r="E234"/>
       <c r="F234" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G234" t="s">
         <v>19</v>
@@ -11552,7 +11553,7 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B235" t="s">
         <v>13</v>
@@ -11565,7 +11566,7 @@
       </c>
       <c r="E235"/>
       <c r="F235" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G235" t="s">
         <v>19</v>
@@ -11582,7 +11583,7 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B236" t="s">
         <v>13</v>
@@ -11594,10 +11595,10 @@
         <v>102</v>
       </c>
       <c r="E236" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G236" t="s">
         <v>19</v>
@@ -11614,7 +11615,7 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B237" t="s">
         <v>13</v>
@@ -11623,13 +11624,13 @@
         <v>14</v>
       </c>
       <c r="D237" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E237" t="s">
+        <v>750</v>
+      </c>
+      <c r="F237" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="F237" s="1" t="s">
-        <v>752</v>
       </c>
       <c r="G237" t="s">
         <v>19</v>
@@ -11646,7 +11647,7 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B238" t="s">
         <v>13</v>
@@ -11659,7 +11660,7 @@
       </c>
       <c r="E238"/>
       <c r="F238" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G238" t="s">
         <v>19</v>
@@ -11676,7 +11677,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B239" t="s">
         <v>13</v>
@@ -11685,13 +11686,13 @@
         <v>14</v>
       </c>
       <c r="D239" t="s">
+        <v>753</v>
+      </c>
+      <c r="E239" t="s">
         <v>754</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>755</v>
-      </c>
-      <c r="F239" t="s">
-        <v>756</v>
       </c>
       <c r="G239" t="s">
         <v>19</v>
@@ -11708,7 +11709,7 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B240" t="s">
         <v>13</v>
@@ -11717,11 +11718,11 @@
         <v>14</v>
       </c>
       <c r="D240" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E240"/>
       <c r="F240" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G240" t="s">
         <v>19</v>
@@ -11738,7 +11739,7 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B241" t="s">
         <v>13</v>
@@ -11750,10 +11751,10 @@
         <v>254</v>
       </c>
       <c r="E241" t="s">
+        <v>758</v>
+      </c>
+      <c r="F241" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="F241" s="1" t="s">
-        <v>760</v>
       </c>
       <c r="G241" t="s">
         <v>19</v>
@@ -11770,7 +11771,7 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B242" t="s">
         <v>13</v>
@@ -11783,7 +11784,7 @@
       </c>
       <c r="E242"/>
       <c r="F242" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G242" t="s">
         <v>19</v>
@@ -11800,7 +11801,7 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B243" t="s">
         <v>13</v>
@@ -11812,10 +11813,10 @@
         <v>254</v>
       </c>
       <c r="E243" t="s">
+        <v>761</v>
+      </c>
+      <c r="F243" t="s">
         <v>762</v>
-      </c>
-      <c r="F243" t="s">
-        <v>763</v>
       </c>
       <c r="G243" t="s">
         <v>19</v>
@@ -11832,7 +11833,7 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B244" t="s">
         <v>13</v>
@@ -11841,11 +11842,11 @@
         <v>14</v>
       </c>
       <c r="D244" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E244"/>
       <c r="F244" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G244" t="s">
         <v>19</v>
@@ -11862,7 +11863,7 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B245" t="s">
         <v>13</v>
@@ -11875,7 +11876,7 @@
       </c>
       <c r="E245"/>
       <c r="F245" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G245" t="s">
         <v>19</v>
@@ -11892,7 +11893,7 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B246" t="s">
         <v>13</v>
@@ -11904,10 +11905,10 @@
         <v>175</v>
       </c>
       <c r="E246" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F246" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G246" t="s">
         <v>19</v>
@@ -11924,7 +11925,7 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B247" t="s">
         <v>13</v>
@@ -11936,10 +11937,10 @@
         <v>175</v>
       </c>
       <c r="E247" t="s">
+        <v>767</v>
+      </c>
+      <c r="F247" t="s">
         <v>768</v>
-      </c>
-      <c r="F247" t="s">
-        <v>769</v>
       </c>
       <c r="G247" t="s">
         <v>19</v>
@@ -11956,7 +11957,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B248" t="s">
         <v>13</v>
@@ -11969,7 +11970,7 @@
       </c>
       <c r="E248"/>
       <c r="F248" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G248" t="s">
         <v>19</v>
@@ -11986,7 +11987,7 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B249" t="s">
         <v>13</v>
@@ -11999,7 +12000,7 @@
       </c>
       <c r="E249"/>
       <c r="F249" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G249" t="s">
         <v>19</v>
@@ -12016,7 +12017,7 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B250" t="s">
         <v>13</v>
@@ -12029,7 +12030,7 @@
       </c>
       <c r="E250"/>
       <c r="F250" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G250" t="s">
         <v>19</v>
@@ -12046,7 +12047,7 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B251" t="s">
         <v>13</v>
@@ -12059,7 +12060,7 @@
       </c>
       <c r="E251"/>
       <c r="F251" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G251" t="s">
         <v>19</v>
@@ -12076,7 +12077,7 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B252" t="s">
         <v>13</v>
@@ -12088,10 +12089,10 @@
         <v>175</v>
       </c>
       <c r="E252" t="s">
+        <v>773</v>
+      </c>
+      <c r="F252" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>775</v>
       </c>
       <c r="G252" t="s">
         <v>19</v>
@@ -12108,7 +12109,7 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B253" t="s">
         <v>13</v>
@@ -12121,7 +12122,7 @@
       </c>
       <c r="E253"/>
       <c r="F253" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G253" t="s">
         <v>19</v>
@@ -12138,7 +12139,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B254" t="s">
         <v>13</v>
@@ -12147,13 +12148,13 @@
         <v>14</v>
       </c>
       <c r="D254" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E254" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G254" t="s">
         <v>19</v>
@@ -12170,7 +12171,7 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B255" t="s">
         <v>13</v>
@@ -12179,11 +12180,11 @@
         <v>14</v>
       </c>
       <c r="D255" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E255"/>
       <c r="F255" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G255" t="s">
         <v>19</v>
@@ -12200,7 +12201,7 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B256" t="s">
         <v>13</v>
@@ -12213,7 +12214,7 @@
       </c>
       <c r="E256"/>
       <c r="F256" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G256" t="s">
         <v>19</v>
@@ -12230,7 +12231,7 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B257" t="s">
         <v>13</v>
@@ -12239,13 +12240,13 @@
         <v>14</v>
       </c>
       <c r="D257" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E257" t="s">
+        <v>929</v>
+      </c>
+      <c r="F257" s="1" t="s">
         <v>930</v>
-      </c>
-      <c r="F257" s="1" t="s">
-        <v>931</v>
       </c>
       <c r="G257" t="s">
         <v>19</v>
@@ -12262,7 +12263,7 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B258" t="s">
         <v>13</v>
@@ -12271,11 +12272,11 @@
         <v>14</v>
       </c>
       <c r="D258" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E258"/>
       <c r="F258" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G258" t="s">
         <v>19</v>
@@ -12292,7 +12293,7 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B259" t="s">
         <v>13</v>
@@ -12301,11 +12302,11 @@
         <v>14</v>
       </c>
       <c r="D259" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E259"/>
       <c r="F259" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G259" t="s">
         <v>19</v>
@@ -12322,7 +12323,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B260" t="s">
         <v>13</v>
@@ -12331,11 +12332,11 @@
         <v>14</v>
       </c>
       <c r="D260" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E260"/>
       <c r="F260" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G260" t="s">
         <v>19</v>
@@ -12352,7 +12353,7 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B261" t="s">
         <v>13</v>
@@ -12361,11 +12362,11 @@
         <v>14</v>
       </c>
       <c r="D261" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E261"/>
       <c r="F261" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G261" t="s">
         <v>19</v>
@@ -12382,7 +12383,7 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B262" t="s">
         <v>13</v>
@@ -12391,13 +12392,13 @@
         <v>14</v>
       </c>
       <c r="D262" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E262" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G262" t="s">
         <v>19</v>
@@ -12414,7 +12415,7 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B263" t="s">
         <v>13</v>
@@ -12423,13 +12424,13 @@
         <v>14</v>
       </c>
       <c r="D263" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E263" t="s">
+        <v>788</v>
+      </c>
+      <c r="F263" t="s">
         <v>789</v>
-      </c>
-      <c r="F263" t="s">
-        <v>790</v>
       </c>
       <c r="G263" t="s">
         <v>19</v>
@@ -12446,7 +12447,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B264" t="s">
         <v>13</v>
@@ -12458,10 +12459,10 @@
         <v>234</v>
       </c>
       <c r="E264" t="s">
+        <v>790</v>
+      </c>
+      <c r="F264" t="s">
         <v>791</v>
-      </c>
-      <c r="F264" t="s">
-        <v>792</v>
       </c>
       <c r="G264" t="s">
         <v>19</v>
@@ -12478,7 +12479,7 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B265" t="s">
         <v>13</v>
@@ -12490,10 +12491,10 @@
         <v>234</v>
       </c>
       <c r="E265" t="s">
+        <v>792</v>
+      </c>
+      <c r="F265" t="s">
         <v>793</v>
-      </c>
-      <c r="F265" t="s">
-        <v>794</v>
       </c>
       <c r="G265" t="s">
         <v>19</v>
@@ -12510,7 +12511,7 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B266" t="s">
         <v>13</v>
@@ -12519,11 +12520,11 @@
         <v>14</v>
       </c>
       <c r="D266" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E266"/>
       <c r="F266" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G266" t="s">
         <v>19</v>
@@ -12540,7 +12541,7 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
@@ -12552,10 +12553,10 @@
         <v>430</v>
       </c>
       <c r="E267" t="s">
+        <v>796</v>
+      </c>
+      <c r="F267" t="s">
         <v>797</v>
-      </c>
-      <c r="F267" t="s">
-        <v>798</v>
       </c>
       <c r="G267" t="s">
         <v>19</v>
@@ -12572,7 +12573,7 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B268" t="s">
         <v>13</v>
@@ -12584,10 +12585,10 @@
         <v>430</v>
       </c>
       <c r="E268" t="s">
+        <v>798</v>
+      </c>
+      <c r="F268" t="s">
         <v>799</v>
-      </c>
-      <c r="F268" t="s">
-        <v>800</v>
       </c>
       <c r="G268" t="s">
         <v>19</v>
@@ -12604,7 +12605,7 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B269" t="s">
         <v>13</v>
@@ -12616,10 +12617,10 @@
         <v>430</v>
       </c>
       <c r="E269" t="s">
+        <v>800</v>
+      </c>
+      <c r="F269" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="F269" s="1" t="s">
-        <v>802</v>
       </c>
       <c r="G269" t="s">
         <v>19</v>
@@ -12636,7 +12637,7 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B270" t="s">
         <v>13</v>
@@ -12648,10 +12649,10 @@
         <v>430</v>
       </c>
       <c r="E270" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F270" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G270" t="s">
         <v>19</v>
@@ -12668,7 +12669,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B271" t="s">
         <v>13</v>
@@ -12680,10 +12681,10 @@
         <v>430</v>
       </c>
       <c r="E271" t="s">
+        <v>803</v>
+      </c>
+      <c r="F271" t="s">
         <v>804</v>
-      </c>
-      <c r="F271" t="s">
-        <v>805</v>
       </c>
       <c r="G271" t="s">
         <v>19</v>
@@ -12700,7 +12701,7 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B272" t="s">
         <v>13</v>
@@ -12713,7 +12714,7 @@
       </c>
       <c r="E272"/>
       <c r="F272" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G272" t="s">
         <v>19</v>
@@ -12730,7 +12731,7 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B273" t="s">
         <v>13</v>
@@ -12742,10 +12743,10 @@
         <v>430</v>
       </c>
       <c r="E273" t="s">
+        <v>806</v>
+      </c>
+      <c r="F273" t="s">
         <v>807</v>
-      </c>
-      <c r="F273" t="s">
-        <v>808</v>
       </c>
       <c r="G273" t="s">
         <v>19</v>
@@ -12762,7 +12763,7 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B274" t="s">
         <v>13</v>
@@ -12774,10 +12775,10 @@
         <v>430</v>
       </c>
       <c r="E274" t="s">
+        <v>808</v>
+      </c>
+      <c r="F274" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="F274" s="1" t="s">
-        <v>810</v>
       </c>
       <c r="G274" t="s">
         <v>19</v>
@@ -12794,7 +12795,7 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B275" t="s">
         <v>13</v>
@@ -12807,7 +12808,7 @@
       </c>
       <c r="E275"/>
       <c r="F275" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G275" t="s">
         <v>19</v>
@@ -12824,7 +12825,7 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B276" t="s">
         <v>13</v>
@@ -12839,7 +12840,7 @@
         <v>440</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G276" t="s">
         <v>19</v>
@@ -12856,7 +12857,7 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B277" t="s">
         <v>13</v>
@@ -12868,10 +12869,10 @@
         <v>430</v>
       </c>
       <c r="E277" t="s">
+        <v>811</v>
+      </c>
+      <c r="F277" s="1" t="s">
         <v>812</v>
-      </c>
-      <c r="F277" s="1" t="s">
-        <v>813</v>
       </c>
       <c r="G277" t="s">
         <v>19</v>
@@ -12888,7 +12889,7 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B278" t="s">
         <v>13</v>
@@ -12901,7 +12902,7 @@
       </c>
       <c r="E278"/>
       <c r="F278" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G278" t="s">
         <v>19</v>
@@ -12918,7 +12919,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B279" t="s">
         <v>13</v>
@@ -12930,10 +12931,10 @@
         <v>430</v>
       </c>
       <c r="E279" t="s">
+        <v>814</v>
+      </c>
+      <c r="F279" t="s">
         <v>815</v>
-      </c>
-      <c r="F279" t="s">
-        <v>816</v>
       </c>
       <c r="G279" t="s">
         <v>19</v>
@@ -12950,7 +12951,7 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B280" t="s">
         <v>13</v>
@@ -12962,10 +12963,10 @@
         <v>430</v>
       </c>
       <c r="E280" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G280" t="s">
         <v>19</v>
@@ -12982,7 +12983,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B281" t="s">
         <v>13</v>
@@ -12995,7 +12996,7 @@
       </c>
       <c r="E281"/>
       <c r="F281" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G281" t="s">
         <v>19</v>
@@ -13012,7 +13013,7 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B282" t="s">
         <v>13</v>
@@ -13024,10 +13025,10 @@
         <v>430</v>
       </c>
       <c r="E282" t="s">
+        <v>818</v>
+      </c>
+      <c r="F282" t="s">
         <v>819</v>
-      </c>
-      <c r="F282" t="s">
-        <v>820</v>
       </c>
       <c r="G282" t="s">
         <v>19</v>
@@ -13044,7 +13045,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B283" t="s">
         <v>13</v>
@@ -13056,10 +13057,10 @@
         <v>430</v>
       </c>
       <c r="E283" t="s">
+        <v>820</v>
+      </c>
+      <c r="F283" s="1" t="s">
         <v>821</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>822</v>
       </c>
       <c r="G283" t="s">
         <v>19</v>
@@ -13076,7 +13077,7 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B284" t="s">
         <v>13</v>
@@ -13088,10 +13089,10 @@
         <v>430</v>
       </c>
       <c r="E284" t="s">
+        <v>822</v>
+      </c>
+      <c r="F284" s="1" t="s">
         <v>823</v>
-      </c>
-      <c r="F284" s="1" t="s">
-        <v>824</v>
       </c>
       <c r="G284" t="s">
         <v>19</v>
@@ -13108,7 +13109,7 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B285" t="s">
         <v>13</v>
@@ -13121,7 +13122,7 @@
       </c>
       <c r="E285"/>
       <c r="F285" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G285" t="s">
         <v>19</v>
@@ -13138,7 +13139,7 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B286" t="s">
         <v>13</v>
@@ -13150,10 +13151,10 @@
         <v>430</v>
       </c>
       <c r="E286" t="s">
+        <v>825</v>
+      </c>
+      <c r="F286" s="1" t="s">
         <v>826</v>
-      </c>
-      <c r="F286" s="1" t="s">
-        <v>827</v>
       </c>
       <c r="G286" t="s">
         <v>19</v>
@@ -13170,7 +13171,7 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B287" t="s">
         <v>13</v>
@@ -13183,7 +13184,7 @@
       </c>
       <c r="E287"/>
       <c r="F287" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G287" t="s">
         <v>19</v>
@@ -13200,7 +13201,7 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B288" t="s">
         <v>13</v>
@@ -13212,10 +13213,10 @@
         <v>430</v>
       </c>
       <c r="E288" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G288" t="s">
         <v>19</v>
@@ -13232,7 +13233,7 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B289" t="s">
         <v>13</v>
@@ -13245,7 +13246,7 @@
       </c>
       <c r="E289"/>
       <c r="F289" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G289" t="s">
         <v>19</v>
@@ -13262,7 +13263,7 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B290" t="s">
         <v>13</v>
@@ -13274,10 +13275,10 @@
         <v>430</v>
       </c>
       <c r="E290" t="s">
+        <v>829</v>
+      </c>
+      <c r="F290" s="1" t="s">
         <v>830</v>
-      </c>
-      <c r="F290" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="G290" t="s">
         <v>19</v>
@@ -13294,7 +13295,7 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B291" t="s">
         <v>13</v>
@@ -13306,10 +13307,10 @@
         <v>430</v>
       </c>
       <c r="E291" t="s">
+        <v>831</v>
+      </c>
+      <c r="F291" t="s">
         <v>832</v>
-      </c>
-      <c r="F291" t="s">
-        <v>833</v>
       </c>
       <c r="G291" t="s">
         <v>19</v>
@@ -13326,7 +13327,7 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B292" t="s">
         <v>13</v>
@@ -13338,10 +13339,10 @@
         <v>430</v>
       </c>
       <c r="E292" t="s">
+        <v>932</v>
+      </c>
+      <c r="F292" s="1" t="s">
         <v>933</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>934</v>
       </c>
       <c r="G292" t="s">
         <v>19</v>
@@ -13358,7 +13359,7 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B293" t="s">
         <v>13</v>
@@ -13371,7 +13372,7 @@
       </c>
       <c r="E293"/>
       <c r="F293" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G293" t="s">
         <v>19</v>
@@ -13388,7 +13389,7 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B294" t="s">
         <v>13</v>
@@ -13400,10 +13401,10 @@
         <v>430</v>
       </c>
       <c r="E294" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F294" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G294" t="s">
         <v>19</v>
@@ -13420,7 +13421,7 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B295" t="s">
         <v>13</v>
@@ -13432,10 +13433,10 @@
         <v>430</v>
       </c>
       <c r="E295" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G295" t="s">
         <v>19</v>
@@ -13452,7 +13453,7 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B296" t="s">
         <v>13</v>
@@ -13464,10 +13465,10 @@
         <v>430</v>
       </c>
       <c r="E296" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F296" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G296" t="s">
         <v>19</v>
@@ -13484,7 +13485,7 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B297" t="s">
         <v>13</v>
@@ -13497,7 +13498,7 @@
       </c>
       <c r="E297"/>
       <c r="F297" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G297" t="s">
         <v>19</v>
@@ -13514,7 +13515,7 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B298" t="s">
         <v>13</v>
@@ -13529,7 +13530,7 @@
         <v>298</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G298" t="s">
         <v>19</v>
@@ -13546,7 +13547,7 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B299" t="s">
         <v>13</v>
@@ -13558,10 +13559,10 @@
         <v>264</v>
       </c>
       <c r="E299" t="s">
+        <v>837</v>
+      </c>
+      <c r="F299" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="F299" s="1" t="s">
-        <v>839</v>
       </c>
       <c r="G299" t="s">
         <v>19</v>
@@ -13578,7 +13579,7 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B300" t="s">
         <v>13</v>
@@ -13590,10 +13591,10 @@
         <v>264</v>
       </c>
       <c r="E300" t="s">
+        <v>839</v>
+      </c>
+      <c r="F300" s="1" t="s">
         <v>840</v>
-      </c>
-      <c r="F300" s="1" t="s">
-        <v>841</v>
       </c>
       <c r="G300" t="s">
         <v>19</v>
@@ -13610,7 +13611,7 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B301" t="s">
         <v>13</v>
@@ -13622,10 +13623,10 @@
         <v>264</v>
       </c>
       <c r="E301" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G301" t="s">
         <v>19</v>
@@ -13642,7 +13643,7 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B302" t="s">
         <v>13</v>
@@ -13654,10 +13655,10 @@
         <v>264</v>
       </c>
       <c r="E302" t="s">
+        <v>842</v>
+      </c>
+      <c r="F302" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>844</v>
       </c>
       <c r="G302" t="s">
         <v>19</v>
@@ -13674,7 +13675,7 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B303" t="s">
         <v>13</v>
@@ -13687,7 +13688,7 @@
       </c>
       <c r="E303"/>
       <c r="F303" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G303" t="s">
         <v>19</v>
@@ -13704,7 +13705,7 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B304" t="s">
         <v>13</v>
@@ -13713,13 +13714,13 @@
         <v>14</v>
       </c>
       <c r="D304" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E304" t="s">
+        <v>845</v>
+      </c>
+      <c r="F304" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="F304" s="1" t="s">
-        <v>847</v>
       </c>
       <c r="G304" t="s">
         <v>19</v>
@@ -13736,7 +13737,7 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B305" t="s">
         <v>13</v>
@@ -13745,11 +13746,11 @@
         <v>14</v>
       </c>
       <c r="D305" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E305"/>
       <c r="F305" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G305" t="s">
         <v>19</v>
@@ -13766,7 +13767,7 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B306" t="s">
         <v>13</v>
@@ -13775,13 +13776,13 @@
         <v>14</v>
       </c>
       <c r="D306" t="s">
+        <v>848</v>
+      </c>
+      <c r="E306" t="s">
         <v>849</v>
       </c>
-      <c r="E306" t="s">
+      <c r="F306" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="F306" s="1" t="s">
-        <v>851</v>
       </c>
       <c r="G306" t="s">
         <v>19</v>
@@ -13798,7 +13799,7 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B307" t="s">
         <v>13</v>
@@ -13807,11 +13808,11 @@
         <v>14</v>
       </c>
       <c r="D307" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E307"/>
       <c r="F307" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G307" t="s">
         <v>19</v>
@@ -13828,7 +13829,7 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B308" t="s">
         <v>13</v>
@@ -13841,7 +13842,7 @@
       </c>
       <c r="E308"/>
       <c r="F308" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G308" t="s">
         <v>19</v>
@@ -13858,7 +13859,7 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B309" t="s">
         <v>13</v>
@@ -13871,7 +13872,7 @@
       </c>
       <c r="E309"/>
       <c r="F309" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G309" t="s">
         <v>19</v>
@@ -13888,7 +13889,7 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B310" t="s">
         <v>13</v>
@@ -13897,13 +13898,13 @@
         <v>14</v>
       </c>
       <c r="D310" t="s">
+        <v>854</v>
+      </c>
+      <c r="E310" t="s">
         <v>855</v>
       </c>
-      <c r="E310" t="s">
-        <v>856</v>
-      </c>
       <c r="F310" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G310" t="s">
         <v>19</v>
@@ -13920,7 +13921,7 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B311" t="s">
         <v>13</v>
@@ -13929,11 +13930,11 @@
         <v>14</v>
       </c>
       <c r="D311" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E311"/>
       <c r="F311" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G311" t="s">
         <v>19</v>
@@ -13950,7 +13951,7 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B312" t="s">
         <v>13</v>
@@ -13959,13 +13960,13 @@
         <v>14</v>
       </c>
       <c r="D312" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E312" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F312" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G312" t="s">
         <v>19</v>
@@ -13982,7 +13983,7 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B313" t="s">
         <v>13</v>
@@ -13991,11 +13992,11 @@
         <v>14</v>
       </c>
       <c r="D313" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E313"/>
       <c r="F313" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G313" t="s">
         <v>19</v>
@@ -14012,7 +14013,7 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B314" t="s">
         <v>13</v>
@@ -14021,11 +14022,11 @@
         <v>14</v>
       </c>
       <c r="D314" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E314"/>
       <c r="F314" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G314" t="s">
         <v>19</v>
@@ -14042,7 +14043,7 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B315" t="s">
         <v>13</v>
@@ -14051,13 +14052,13 @@
         <v>14</v>
       </c>
       <c r="D315" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E315" t="s">
+        <v>860</v>
+      </c>
+      <c r="F315" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="F315" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="G315" t="s">
         <v>19</v>
@@ -14074,7 +14075,7 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B316" t="s">
         <v>13</v>
@@ -14083,11 +14084,11 @@
         <v>14</v>
       </c>
       <c r="D316" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E316"/>
       <c r="F316" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G316" t="s">
         <v>19</v>
@@ -14104,7 +14105,7 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B317" t="s">
         <v>13</v>
@@ -14117,7 +14118,7 @@
       </c>
       <c r="E317"/>
       <c r="F317" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G317" t="s">
         <v>19</v>
@@ -14134,7 +14135,7 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B318" t="s">
         <v>13</v>
@@ -14147,7 +14148,7 @@
       </c>
       <c r="E318"/>
       <c r="F318" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G318" t="s">
         <v>19</v>
@@ -14164,7 +14165,7 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B319" t="s">
         <v>13</v>
@@ -14177,7 +14178,7 @@
       </c>
       <c r="E319"/>
       <c r="F319" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G319" t="s">
         <v>19</v>
@@ -14194,7 +14195,7 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B320" t="s">
         <v>13</v>
@@ -14206,10 +14207,10 @@
         <v>70</v>
       </c>
       <c r="E320" t="s">
+        <v>866</v>
+      </c>
+      <c r="F320" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="F320" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="G320" t="s">
         <v>19</v>
@@ -14226,7 +14227,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B321" t="s">
         <v>13</v>
@@ -14235,13 +14236,13 @@
         <v>14</v>
       </c>
       <c r="D321" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E321" t="s">
+        <v>868</v>
+      </c>
+      <c r="F321" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="F321" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="G321" t="s">
         <v>19</v>
@@ -14258,7 +14259,7 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B322" t="s">
         <v>13</v>
@@ -14267,13 +14268,13 @@
         <v>14</v>
       </c>
       <c r="D322" t="s">
+        <v>870</v>
+      </c>
+      <c r="E322" t="s">
         <v>871</v>
       </c>
-      <c r="E322" t="s">
+      <c r="F322" s="1" t="s">
         <v>872</v>
-      </c>
-      <c r="F322" s="1" t="s">
-        <v>873</v>
       </c>
       <c r="G322" t="s">
         <v>19</v>
@@ -14290,7 +14291,7 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B323" t="s">
         <v>13</v>
@@ -14299,11 +14300,11 @@
         <v>14</v>
       </c>
       <c r="D323" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E323"/>
       <c r="F323" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G323" t="s">
         <v>19</v>
@@ -14320,7 +14321,7 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B324" t="s">
         <v>13</v>
@@ -14329,13 +14330,13 @@
         <v>14</v>
       </c>
       <c r="D324" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E324" t="s">
+        <v>874</v>
+      </c>
+      <c r="F324" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="F324" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="G324" t="s">
         <v>19</v>
@@ -14352,7 +14353,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B325" t="s">
         <v>13</v>
@@ -14361,11 +14362,11 @@
         <v>14</v>
       </c>
       <c r="D325" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E325"/>
       <c r="F325" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G325" t="s">
         <v>19</v>
@@ -14382,7 +14383,7 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B326" t="s">
         <v>13</v>
@@ -14391,11 +14392,11 @@
         <v>14</v>
       </c>
       <c r="D326" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E326"/>
       <c r="F326" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G326" t="s">
         <v>19</v>
@@ -14412,7 +14413,7 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B327" t="s">
         <v>13</v>
@@ -14421,13 +14422,13 @@
         <v>14</v>
       </c>
       <c r="D327" t="s">
+        <v>879</v>
+      </c>
+      <c r="E327" t="s">
         <v>880</v>
       </c>
-      <c r="E327" t="s">
+      <c r="F327" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="F327" s="1" t="s">
-        <v>882</v>
       </c>
       <c r="G327" t="s">
         <v>19</v>
@@ -14444,7 +14445,7 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B328" t="s">
         <v>13</v>
@@ -14453,13 +14454,13 @@
         <v>14</v>
       </c>
       <c r="D328" t="s">
+        <v>882</v>
+      </c>
+      <c r="E328" t="s">
         <v>883</v>
       </c>
-      <c r="E328" t="s">
+      <c r="F328" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="F328" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="G328" t="s">
         <v>19</v>
@@ -14476,7 +14477,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B329" t="s">
         <v>13</v>
@@ -14485,11 +14486,11 @@
         <v>14</v>
       </c>
       <c r="D329" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E329"/>
       <c r="F329" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G329" t="s">
         <v>19</v>
@@ -14506,7 +14507,7 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B330" t="s">
         <v>13</v>
@@ -14515,13 +14516,13 @@
         <v>14</v>
       </c>
       <c r="D330" t="s">
+        <v>887</v>
+      </c>
+      <c r="E330" t="s">
         <v>888</v>
       </c>
-      <c r="E330" t="s">
+      <c r="F330" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="G330" t="s">
         <v>19</v>
@@ -14538,7 +14539,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B331" t="s">
         <v>13</v>
@@ -14547,13 +14548,13 @@
         <v>14</v>
       </c>
       <c r="D331" t="s">
+        <v>890</v>
+      </c>
+      <c r="E331" t="s">
         <v>891</v>
       </c>
-      <c r="E331" t="s">
+      <c r="F331" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="F331" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="G331" t="s">
         <v>19</v>
@@ -14570,7 +14571,7 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B332" t="s">
         <v>13</v>
@@ -14579,13 +14580,13 @@
         <v>14</v>
       </c>
       <c r="D332" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E332" t="s">
+        <v>893</v>
+      </c>
+      <c r="F332" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="F332" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="G332" t="s">
         <v>19</v>
@@ -14602,7 +14603,7 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B333" t="s">
         <v>13</v>
@@ -14611,11 +14612,11 @@
         <v>14</v>
       </c>
       <c r="D333" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E333"/>
       <c r="F333" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G333" t="s">
         <v>19</v>
@@ -14632,7 +14633,7 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B334" t="s">
         <v>13</v>
@@ -14641,13 +14642,13 @@
         <v>14</v>
       </c>
       <c r="D334" t="s">
+        <v>897</v>
+      </c>
+      <c r="E334" t="s">
         <v>898</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="F334" s="1" t="s">
-        <v>900</v>
       </c>
       <c r="G334" t="s">
         <v>19</v>
@@ -14664,7 +14665,7 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B335" t="s">
         <v>13</v>
@@ -14673,13 +14674,13 @@
         <v>14</v>
       </c>
       <c r="D335" t="s">
+        <v>900</v>
+      </c>
+      <c r="E335" t="s">
         <v>901</v>
       </c>
-      <c r="E335" t="s">
+      <c r="F335" s="1" t="s">
         <v>902</v>
-      </c>
-      <c r="F335" s="1" t="s">
-        <v>903</v>
       </c>
       <c r="G335" t="s">
         <v>19</v>
@@ -14696,7 +14697,7 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B336" t="s">
         <v>13</v>
@@ -14708,10 +14709,10 @@
         <v>123</v>
       </c>
       <c r="E336" t="s">
+        <v>903</v>
+      </c>
+      <c r="F336" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="F336" s="1" t="s">
-        <v>905</v>
       </c>
       <c r="G336" t="s">
         <v>19</v>
@@ -14728,7 +14729,7 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B337" t="s">
         <v>13</v>
@@ -14740,10 +14741,10 @@
         <v>123</v>
       </c>
       <c r="E337" t="s">
+        <v>905</v>
+      </c>
+      <c r="F337" s="1" t="s">
         <v>906</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>907</v>
       </c>
       <c r="G337" t="s">
         <v>19</v>
@@ -14760,7 +14761,7 @@
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B338" t="s">
         <v>13</v>
@@ -14772,10 +14773,10 @@
         <v>123</v>
       </c>
       <c r="E338" t="s">
+        <v>907</v>
+      </c>
+      <c r="F338" s="1" t="s">
         <v>908</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>909</v>
       </c>
       <c r="G338" t="s">
         <v>19</v>
@@ -14792,7 +14793,7 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B339" t="s">
         <v>13</v>
@@ -14804,10 +14805,10 @@
         <v>123</v>
       </c>
       <c r="E339" t="s">
+        <v>909</v>
+      </c>
+      <c r="F339" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="F339" s="1" t="s">
-        <v>911</v>
       </c>
       <c r="G339" t="s">
         <v>19</v>
@@ -14824,7 +14825,7 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B340" t="s">
         <v>13</v>
@@ -14836,10 +14837,10 @@
         <v>88</v>
       </c>
       <c r="E340" t="s">
+        <v>911</v>
+      </c>
+      <c r="F340" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="F340" s="1" t="s">
-        <v>913</v>
       </c>
       <c r="G340" t="s">
         <v>19</v>
@@ -14856,7 +14857,7 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B341" t="s">
         <v>13</v>
@@ -14865,13 +14866,13 @@
         <v>14</v>
       </c>
       <c r="D341" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E341" t="s">
+        <v>913</v>
+      </c>
+      <c r="F341" s="1" t="s">
         <v>914</v>
-      </c>
-      <c r="F341" s="1" t="s">
-        <v>915</v>
       </c>
       <c r="G341" t="s">
         <v>19</v>
@@ -14888,7 +14889,7 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B342" t="s">
         <v>13</v>
@@ -14900,10 +14901,10 @@
         <v>99</v>
       </c>
       <c r="E342" t="s">
+        <v>915</v>
+      </c>
+      <c r="F342" t="s">
         <v>916</v>
-      </c>
-      <c r="F342" t="s">
-        <v>917</v>
       </c>
       <c r="G342" t="s">
         <v>19</v>
@@ -15025,6 +15026,7 @@
     <hyperlink ref="F236" r:id="rId102" xr:uid="{57FE0DAA-AB11-436C-93D1-94925AA217E5}"/>
     <hyperlink ref="F275" r:id="rId103" xr:uid="{C9260396-C81F-43AE-8140-AF36972DFE57}"/>
     <hyperlink ref="H163" r:id="rId104" xr:uid="{5BFBA6A0-6CB8-47F6-A1B2-D6696E0A3326}"/>
+    <hyperlink ref="J122" r:id="rId105" xr:uid="{91B5C5CC-D039-4D6D-A53C-96732530C258}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/collected-data.xlsx
+++ b/collected-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-26.04\home\leo\OS-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E070EF-40DA-4B39-9A41-2F7BC3042639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DFC056-8FF7-445B-8CE6-484A5082A82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="528" windowWidth="26784" windowHeight="16032" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3083" uniqueCount="952">
   <si>
     <t>年份</t>
   </si>
@@ -211,9 +211,6 @@
     <t>Alien</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/202310007101563/Alien</t>
-  </si>
-  <si>
     <t>需登录/不可公开确认</t>
   </si>
   <si>
@@ -304,12 +301,6 @@
     <t>只敲代码不玩耍聪明baka也变傻ᗜˬᗜ</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/bakaos</t>
-  </si>
-  <si>
-    <t>不可匿名访问；本地未clone</t>
-  </si>
-  <si>
     <t>广东工业大学</t>
   </si>
   <si>
@@ -484,15 +475,9 @@
     <t>https://gitlab.eduxiji.net/educg-group-22024-2210153/T202418123993075-3283</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-26010-2376550/T202418123993075-2940</t>
-  </si>
-  <si>
     <t>Chronix</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/T202518123995568/oskernel2025-chronix-retest</t>
-  </si>
-  <si>
     <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/T202518123995568-675</t>
   </si>
   <si>
@@ -994,15 +979,6 @@
     <t>https://gitlab.eduxiji.net/educg-group-14238-914330/qianpinyi-377</t>
   </si>
   <si>
-    <t>学到东西就算胜利队</t>
-  </si>
-  <si>
-    <t>https://gitlab.eduxiji.net/educg-group-22024-2210153/T202410287992637-2601</t>
-  </si>
-  <si>
-    <t>https://gitlab.eduxiji.net/educg-group-26010-2376550/T202410287992637-1454</t>
-  </si>
-  <si>
     <t>undefinedType</t>
   </si>
   <si>
@@ -1054,15 +1030,6 @@
     <t>WHW</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-12100-765609/1911570-1951</t>
-  </si>
-  <si>
-    <t>https://gitlab.eduxiji.net/wsy/oskernel2022-whw.git</t>
-  </si>
-  <si>
-    <t>https://gitlab.eduxiji.net/educg-group-14238-914330/1911570-1414</t>
-  </si>
-  <si>
     <t>萌新</t>
   </si>
   <si>
@@ -1153,9 +1120,6 @@
     <t>Starry Mix</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/starry-mix</t>
-  </si>
-  <si>
     <t>上海海事大学</t>
   </si>
   <si>
@@ -1354,9 +1318,6 @@
     <t>https://github.com/KidsZZ/F7LY</t>
   </si>
   <si>
-    <t>可访问；以 GitHub 完整镜像为准</t>
-  </si>
-  <si>
     <t>RuOK</t>
   </si>
   <si>
@@ -1624,9 +1585,6 @@
     <t>https://gitlab.eduxiji.net/educg-group-22024-2210153/T202411117993110-222</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-26010-2376550/T202411117993110-198</t>
-  </si>
-  <si>
     <t>长春理工大学</t>
   </si>
   <si>
@@ -1693,9 +1651,6 @@
     <t>https://gitlab.eduxiji.net/educg-group-12100-765609/2022os-c-core</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/c-core1/2022os-c-core.git</t>
-  </si>
-  <si>
     <t>https://gitlab.eduxiji.net/educg-group-14239-914332/2022os-c-core</t>
   </si>
   <si>
@@ -1732,9 +1687,6 @@
     <t>文火土豆丝</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/potato-kernal/cy-os</t>
-  </si>
-  <si>
     <t>中南大学</t>
   </si>
   <si>
@@ -1786,19 +1738,10 @@
     <t>阁下如何应队</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/lightenos/oskernel2025-lightenos</t>
-  </si>
-  <si>
-    <t>https://gitlab.eduxiji.net/educg-group-38066-3006609/T202511660997962-2144</t>
-  </si>
-  <si>
     <t>重庆师范大学</t>
   </si>
   <si>
     <t>小骨头</t>
-  </si>
-  <si>
-    <t>https://gitlab.eduxiji.net/hzc1998/oskernel2021-xbook2</t>
   </si>
   <si>
     <t>重庆邮电大学</t>
@@ -2867,6 +2810,122 @@
   </si>
   <si>
     <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/T202510486995205-1539</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/hzc1998/oskernel2021-xbook2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/lightenos/oskernel2025-lightenos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-38066-3006609/T202511660997962-2144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可访问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已私密/删库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/potato-kernal/cy-os</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/c-core1/2022os-c-core.git</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-26010-2376550/T202411117993110-198</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可访问；以 GitHub 完整镜像为最新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/starry-mix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/T202518123995568/oskernel2025-chronix-retest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/T202519145995201/bakaos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-36002-2710490/T202519145995201-2682</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挖出来的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/202310007101563/Alien</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/ChenRuiwei/Phoenix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/oscomp/first-prize-osk2024-phoenix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可访问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学到东西就算胜利队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-22024-2210153/T202410287992637-2601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/T202410287992637/oskernel2024-galaxyos</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-26010-2376550/T202410287992637-1454</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-12100-765609/1911570-1951</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-14238-914330/1911570-1414</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/wsy/oskernel2022-whw.git</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已私密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/T202510003996120/starry-mix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3841,11 +3900,11 @@
       <c r="G16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
@@ -3866,25 +3925,25 @@
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -3904,25 +3963,25 @@
         <v>14</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -3939,26 +3998,26 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -3978,17 +4037,17 @@
         <v>14</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>19</v>
@@ -4012,17 +4071,17 @@
         <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>19</v>
@@ -4046,17 +4105,17 @@
         <v>14</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>19</v>
@@ -4080,25 +4139,25 @@
         <v>14</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -4118,26 +4177,30 @@
         <v>14</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="1" t="s">
+        <v>935</v>
+      </c>
       <c r="I24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>94</v>
+        <v>926</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>936</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L24" s="3"/>
+        <v>926</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>937</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
     </row>
@@ -4152,17 +4215,17 @@
         <v>14</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>19</v>
@@ -4186,17 +4249,17 @@
         <v>14</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>19</v>
@@ -4220,25 +4283,25 @@
         <v>14</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="I27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>19</v>
@@ -4258,7 +4321,7 @@
         <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>26</v>
@@ -4268,7 +4331,7 @@
         <v>17</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>19</v>
@@ -4292,25 +4355,25 @@
         <v>14</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>19</v>
@@ -4330,25 +4393,25 @@
         <v>14</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>19</v>
@@ -4368,25 +4431,25 @@
         <v>14</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>19</v>
@@ -4406,23 +4469,23 @@
         <v>14</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>19</v>
@@ -4442,17 +4505,17 @@
         <v>14</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>19</v>
@@ -4476,17 +4539,17 @@
         <v>14</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>19</v>
@@ -4510,25 +4573,25 @@
         <v>14</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>19</v>
@@ -4548,25 +4611,25 @@
         <v>14</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>19</v>
@@ -4586,25 +4649,25 @@
         <v>14</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="I37" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>19</v>
@@ -4624,25 +4687,25 @@
         <v>14</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>19</v>
@@ -4662,17 +4725,17 @@
         <v>14</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>19</v>
@@ -4696,17 +4759,17 @@
         <v>14</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>19</v>
@@ -4730,17 +4793,17 @@
         <v>14</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>19</v>
@@ -4764,26 +4827,28 @@
         <v>14</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="3"/>
+      <c r="H42" s="1" t="s">
+        <v>939</v>
+      </c>
       <c r="I42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>154</v>
+        <v>940</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>95</v>
+        <v>926</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -4800,23 +4865,23 @@
         <v>14</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>156</v>
+      <c r="H43" s="1" t="s">
+        <v>934</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>19</v>
@@ -4836,10 +4901,10 @@
         <v>14</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
@@ -4850,7 +4915,7 @@
         <v>17</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>19</v>
@@ -4870,23 +4935,23 @@
         <v>14</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>19</v>
@@ -4906,23 +4971,23 @@
         <v>14</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>19</v>
@@ -4942,25 +5007,25 @@
         <v>14</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>19</v>
@@ -4980,23 +5045,23 @@
         <v>14</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>19</v>
@@ -5016,25 +5081,25 @@
         <v>14</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>19</v>
@@ -5054,25 +5119,25 @@
         <v>14</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="F50" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>19</v>
@@ -5092,17 +5157,17 @@
         <v>14</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>19</v>
@@ -5126,17 +5191,17 @@
         <v>14</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>19</v>
@@ -5160,25 +5225,25 @@
         <v>14</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>19</v>
@@ -5198,23 +5263,23 @@
         <v>14</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>19</v>
@@ -5234,23 +5299,23 @@
         <v>14</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>19</v>
@@ -5270,23 +5335,23 @@
         <v>14</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>19</v>
@@ -5306,25 +5371,25 @@
         <v>14</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>19</v>
@@ -5344,17 +5409,17 @@
         <v>14</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>19</v>
@@ -5378,25 +5443,25 @@
         <v>14</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>19</v>
@@ -5416,13 +5481,13 @@
         <v>14</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>19</v>
@@ -5432,7 +5497,7 @@
         <v>17</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>19</v>
@@ -5452,13 +5517,13 @@
         <v>14</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>19</v>
@@ -5468,7 +5533,7 @@
         <v>17</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>19</v>
@@ -5488,25 +5553,25 @@
         <v>14</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>19</v>
@@ -5526,25 +5591,25 @@
         <v>14</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>19</v>
@@ -5564,17 +5629,17 @@
         <v>14</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>19</v>
@@ -5598,25 +5663,25 @@
         <v>14</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K65" s="3" t="s">
         <v>19</v>
@@ -5636,25 +5701,25 @@
         <v>14</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>19</v>
@@ -5671,13 +5736,13 @@
         <v>13</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -5688,7 +5753,7 @@
         <v>17</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K67" s="3" t="s">
         <v>19</v>
@@ -5708,25 +5773,25 @@
         <v>14</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>19</v>
@@ -5743,26 +5808,26 @@
         <v>13</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>19</v>
@@ -5782,23 +5847,23 @@
         <v>14</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>19</v>
@@ -5818,25 +5883,25 @@
         <v>14</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>19</v>
@@ -5856,25 +5921,25 @@
         <v>14</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>19</v>
@@ -5894,27 +5959,27 @@
         <v>14</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
@@ -5930,25 +5995,25 @@
         <v>14</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="G74" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>19</v>
@@ -5968,17 +6033,17 @@
         <v>14</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>19</v>
@@ -6002,17 +6067,17 @@
         <v>14</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>19</v>
@@ -6036,25 +6101,25 @@
         <v>14</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>19</v>
@@ -6074,25 +6139,25 @@
         <v>14</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>19</v>
@@ -6112,25 +6177,25 @@
         <v>14</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K79" s="3" t="s">
         <v>19</v>
@@ -6150,25 +6215,25 @@
         <v>14</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>19</v>
@@ -6188,23 +6253,23 @@
         <v>14</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>19</v>
@@ -6224,23 +6289,23 @@
         <v>14</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>19</v>
@@ -6257,13 +6322,13 @@
         <v>13</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
@@ -6274,7 +6339,7 @@
         <v>17</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>19</v>
@@ -6291,26 +6356,26 @@
         <v>13</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>19</v>
@@ -6327,26 +6392,26 @@
         <v>13</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>19</v>
@@ -6366,25 +6431,25 @@
         <v>14</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>19</v>
@@ -6404,23 +6469,23 @@
         <v>14</v>
       </c>
       <c r="D87" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>19</v>
@@ -6440,25 +6505,25 @@
         <v>14</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>19</v>
@@ -6478,25 +6543,25 @@
         <v>14</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>19</v>
@@ -6516,26 +6581,28 @@
         <v>14</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>325</v>
+        <v>942</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>943</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H90" s="3"/>
+      <c r="H90" s="1" t="s">
+        <v>944</v>
+      </c>
       <c r="I90" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>326</v>
+        <v>926</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>945</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>19</v>
+        <v>941</v>
       </c>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
@@ -6552,25 +6619,25 @@
         <v>14</v>
       </c>
       <c r="D91" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="F91" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>19</v>
@@ -6590,25 +6657,25 @@
         <v>14</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>19</v>
@@ -6628,17 +6695,17 @@
         <v>14</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>19</v>
@@ -6662,25 +6729,25 @@
         <v>14</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>19</v>
@@ -6700,25 +6767,25 @@
         <v>14</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>344</v>
+        <v>335</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>946</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>345</v>
+      <c r="H95" s="1" t="s">
+        <v>948</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>346</v>
+        <v>949</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>947</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>19</v>
@@ -6738,25 +6805,25 @@
         <v>14</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="F96" s="3" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>19</v>
@@ -6776,23 +6843,23 @@
         <v>14</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>19</v>
@@ -6812,23 +6879,23 @@
         <v>14</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>19</v>
@@ -6848,25 +6915,25 @@
         <v>14</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="K99" s="3" t="s">
         <v>19</v>
@@ -6886,17 +6953,17 @@
         <v>14</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>19</v>
@@ -6920,25 +6987,25 @@
         <v>14</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>19</v>
@@ -6958,17 +7025,17 @@
         <v>14</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>19</v>
@@ -6992,23 +7059,23 @@
         <v>14</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>19</v>
@@ -7028,24 +7095,26 @@
         <v>14</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="3"/>
+      <c r="H104" s="1" t="s">
+        <v>950</v>
+      </c>
       <c r="I104" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>377</v>
+        <v>926</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>933</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>64</v>
+        <v>951</v>
       </c>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
@@ -7062,25 +7131,25 @@
         <v>14</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="K105" s="3" t="s">
         <v>19</v>
@@ -7100,17 +7169,17 @@
         <v>14</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>19</v>
@@ -7134,17 +7203,17 @@
         <v>14</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>19</v>
@@ -7168,25 +7237,25 @@
         <v>14</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>19</v>
@@ -7206,25 +7275,25 @@
         <v>14</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>19</v>
@@ -7244,13 +7313,13 @@
         <v>14</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>19</v>
@@ -7260,7 +7329,7 @@
         <v>17</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="K110" s="3" t="s">
         <v>19</v>
@@ -7280,23 +7349,23 @@
         <v>14</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="K111" s="3" t="s">
         <v>19</v>
@@ -7316,25 +7385,25 @@
         <v>14</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>19</v>
@@ -7354,25 +7423,25 @@
         <v>14</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>19</v>
@@ -7392,25 +7461,25 @@
         <v>14</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>19</v>
@@ -7430,25 +7499,25 @@
         <v>14</v>
       </c>
       <c r="D115" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J115" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>422</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>19</v>
@@ -7468,23 +7537,23 @@
         <v>14</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="K116" s="3" t="s">
         <v>19</v>
@@ -7504,23 +7573,23 @@
         <v>14</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="K117" s="3" t="s">
         <v>19</v>
@@ -7540,17 +7609,17 @@
         <v>14</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>19</v>
@@ -7574,25 +7643,25 @@
         <v>14</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="K119" s="3" t="s">
         <v>19</v>
@@ -7612,23 +7681,23 @@
         <v>14</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>19</v>
@@ -7648,10 +7717,10 @@
         <v>14</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="3" t="s">
@@ -7662,7 +7731,7 @@
         <v>17</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="K121" s="3" t="s">
         <v>19</v>
@@ -7682,23 +7751,23 @@
         <v>14</v>
       </c>
       <c r="D122" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E122" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>444</v>
+        <v>932</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="K122" s="3" t="s">
         <v>19</v>
@@ -7718,23 +7787,23 @@
         <v>14</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="K123" s="3" t="s">
         <v>19</v>
@@ -7754,23 +7823,23 @@
         <v>14</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="K124" s="3" t="s">
         <v>19</v>
@@ -7787,26 +7856,26 @@
         <v>13</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="K125" s="3" t="s">
         <v>19</v>
@@ -7823,26 +7892,26 @@
         <v>13</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>19</v>
@@ -7859,13 +7928,13 @@
         <v>13</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
@@ -7876,7 +7945,7 @@
         <v>17</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>19</v>
@@ -7893,26 +7962,26 @@
         <v>13</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="K128" s="3" t="s">
         <v>19</v>
@@ -7929,26 +7998,26 @@
         <v>13</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="K129" s="3" t="s">
         <v>19</v>
@@ -7968,25 +8037,25 @@
         <v>14</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="K130" s="3" t="s">
         <v>19</v>
@@ -8006,23 +8075,23 @@
         <v>14</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="K131" s="3" t="s">
         <v>19</v>
@@ -8042,17 +8111,17 @@
         <v>14</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>19</v>
@@ -8073,26 +8142,26 @@
         <v>13</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="F133" s="3"/>
       <c r="G133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="K133" s="3" t="s">
         <v>19</v>
@@ -8112,25 +8181,25 @@
         <v>14</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="K134" s="3" t="s">
         <v>19</v>
@@ -8150,17 +8219,17 @@
         <v>14</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>19</v>
@@ -8184,25 +8253,25 @@
         <v>14</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="K136" s="3" t="s">
         <v>19</v>
@@ -8222,17 +8291,17 @@
         <v>14</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>19</v>
@@ -8256,25 +8325,25 @@
         <v>14</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="K138" s="3" t="s">
         <v>19</v>
@@ -8294,17 +8363,17 @@
         <v>14</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F139" s="3"/>
       <c r="G139" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>19</v>
@@ -8328,25 +8397,25 @@
         <v>14</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>19</v>
@@ -8366,25 +8435,25 @@
         <v>14</v>
       </c>
       <c r="D141" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="E141" s="3" t="s">
-        <v>504</v>
-      </c>
       <c r="F141" s="3" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="K141" s="3" t="s">
         <v>19</v>
@@ -8404,23 +8473,23 @@
         <v>14</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="K142" s="3" t="s">
         <v>19</v>
@@ -8440,10 +8509,10 @@
         <v>14</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="3" t="s">
@@ -8454,7 +8523,7 @@
         <v>17</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="K143" s="3" t="s">
         <v>19</v>
@@ -8471,26 +8540,26 @@
         <v>13</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="F144" s="3"/>
       <c r="G144" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="K144" s="3" t="s">
         <v>19</v>
@@ -8507,13 +8576,13 @@
         <v>13</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="3" t="s">
@@ -8524,7 +8593,7 @@
         <v>17</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="K145" s="3" t="s">
         <v>19</v>
@@ -8541,26 +8610,26 @@
         <v>13</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J146" s="3" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="K146" s="3" t="s">
         <v>19</v>
@@ -8577,26 +8646,26 @@
         <v>13</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="K147" s="3" t="s">
         <v>19</v>
@@ -8613,26 +8682,26 @@
         <v>13</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="K148" s="3" t="s">
         <v>19</v>
@@ -8652,23 +8721,23 @@
         <v>14</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="F149" s="3"/>
       <c r="G149" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="K149" s="3" t="s">
         <v>19</v>
@@ -8688,13 +8757,13 @@
         <v>14</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>19</v>
@@ -8703,8 +8772,8 @@
       <c r="I150" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J150" s="3" t="s">
-        <v>534</v>
+      <c r="J150" s="1" t="s">
+        <v>931</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>19</v>
@@ -8724,25 +8793,25 @@
         <v>14</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="K151" s="3" t="s">
         <v>19</v>
@@ -8762,25 +8831,25 @@
         <v>14</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="G152" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="K152" s="3" t="s">
         <v>19</v>
@@ -8800,23 +8869,23 @@
         <v>14</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="F153" s="3"/>
       <c r="G153" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="K153" s="3" t="s">
         <v>19</v>
@@ -8836,17 +8905,17 @@
         <v>14</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="F154" s="3"/>
       <c r="G154" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>19</v>
@@ -8870,17 +8939,17 @@
         <v>14</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="F155" s="3"/>
       <c r="G155" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>19</v>
@@ -8904,25 +8973,25 @@
         <v>14</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H156" s="3" t="s">
-        <v>557</v>
+      <c r="H156" s="1" t="s">
+        <v>929</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>140</v>
+        <v>930</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>19</v>
@@ -8942,17 +9011,17 @@
         <v>14</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>19</v>
@@ -8976,17 +9045,17 @@
         <v>14</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>19</v>
@@ -9010,25 +9079,25 @@
         <v>14</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="K159" s="3" t="s">
         <v>19</v>
@@ -9048,20 +9117,20 @@
         <v>14</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H160" s="3" t="s">
-        <v>570</v>
+      <c r="H160" s="1" t="s">
+        <v>928</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J160" s="3"/>
       <c r="K160" s="3" t="s">
@@ -9082,25 +9151,25 @@
         <v>14</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="K161" s="3" t="s">
         <v>19</v>
@@ -9120,17 +9189,17 @@
         <v>14</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>19</v>
@@ -9154,23 +9223,23 @@
         <v>14</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="K163" s="3" t="s">
         <v>19</v>
@@ -9190,23 +9259,23 @@
         <v>14</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="K164" s="3" t="s">
         <v>19</v>
@@ -9226,17 +9295,17 @@
         <v>14</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>19</v>
@@ -9257,26 +9326,26 @@
         <v>13</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H166" s="3" t="s">
-        <v>588</v>
+      <c r="H166" s="1" t="s">
+        <v>924</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J166" s="3" t="s">
-        <v>589</v>
+        <v>926</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>925</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>19</v>
@@ -9296,20 +9365,20 @@
         <v>14</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H167" s="3" t="s">
-        <v>592</v>
+      <c r="H167" s="1" t="s">
+        <v>923</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>64</v>
+        <v>927</v>
       </c>
       <c r="J167" s="3"/>
       <c r="K167" s="3" t="s">
@@ -9330,17 +9399,17 @@
         <v>14</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>19</v>
@@ -9364,13 +9433,13 @@
         <v>14</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>19</v>
@@ -9398,13 +9467,13 @@
         <v>14</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>19</v>
@@ -9432,13 +9501,13 @@
         <v>14</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>19</v>
@@ -9466,13 +9535,13 @@
         <v>14</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>19</v>
@@ -9500,13 +9569,13 @@
         <v>14</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>19</v>
@@ -9534,13 +9603,13 @@
         <v>14</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>608</v>
+        <v>589</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>610</v>
+        <v>591</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>19</v>
@@ -9568,13 +9637,13 @@
         <v>14</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>611</v>
+        <v>592</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>19</v>
@@ -9602,13 +9671,13 @@
         <v>14</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>19</v>
@@ -9636,13 +9705,13 @@
         <v>14</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>19</v>
@@ -9670,13 +9739,13 @@
         <v>14</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>19</v>
@@ -9704,13 +9773,13 @@
         <v>14</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>19</v>
@@ -9738,13 +9807,13 @@
         <v>14</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>623</v>
+        <v>604</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>19</v>
@@ -9772,13 +9841,13 @@
         <v>14</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>626</v>
+        <v>607</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>19</v>
@@ -9806,13 +9875,13 @@
         <v>14</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>19</v>
@@ -9840,13 +9909,13 @@
         <v>14</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>19</v>
@@ -9874,13 +9943,13 @@
         <v>14</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>19</v>
@@ -9908,19 +9977,19 @@
         <v>14</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>635</v>
+        <v>616</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>19</v>
@@ -9947,16 +10016,16 @@
         <v>43</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>19</v>
@@ -9980,19 +10049,19 @@
         <v>14</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>19</v>
@@ -10016,13 +10085,13 @@
         <v>14</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>643</v>
+        <v>624</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>644</v>
+        <v>625</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>19</v>
@@ -10050,19 +10119,19 @@
         <v>14</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>645</v>
+        <v>626</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>647</v>
+        <v>628</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>19</v>
@@ -10086,19 +10155,19 @@
         <v>14</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>648</v>
+        <v>629</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>649</v>
+        <v>630</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>650</v>
+        <v>631</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>19</v>
@@ -10122,19 +10191,19 @@
         <v>14</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>651</v>
+        <v>632</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>652</v>
+        <v>633</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>653</v>
+        <v>634</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>19</v>
@@ -10158,19 +10227,19 @@
         <v>14</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>655</v>
+        <v>636</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>656</v>
+        <v>637</v>
       </c>
       <c r="G192" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>657</v>
+        <v>638</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>19</v>
@@ -10194,19 +10263,19 @@
         <v>14</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>658</v>
+        <v>639</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>659</v>
+        <v>640</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>660</v>
+        <v>641</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>661</v>
+        <v>642</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>19</v>
@@ -10230,19 +10299,19 @@
         <v>14</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>662</v>
+        <v>643</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>664</v>
+        <v>645</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>19</v>
@@ -10269,16 +10338,16 @@
         <v>61</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>665</v>
+        <v>646</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>19</v>
@@ -10305,16 +10374,16 @@
         <v>25</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>670</v>
+        <v>651</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>19</v>
@@ -10338,19 +10407,19 @@
         <v>14</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>19</v>
@@ -10374,19 +10443,19 @@
         <v>14</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>674</v>
+        <v>655</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>19</v>
@@ -10410,19 +10479,19 @@
         <v>14</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>678</v>
+        <v>659</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>679</v>
+        <v>660</v>
       </c>
       <c r="I199" s="3" t="s">
         <v>19</v>
@@ -10449,16 +10518,16 @@
         <v>25</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="G200" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>19</v>
@@ -10482,19 +10551,19 @@
         <v>14</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>685</v>
+        <v>666</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>19</v>
@@ -10518,19 +10587,19 @@
         <v>14</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>686</v>
+        <v>667</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>688</v>
+        <v>669</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>19</v>
@@ -10545,7 +10614,7 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B203" t="s">
         <v>13</v>
@@ -10557,10 +10626,10 @@
         <v>15</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="G203" t="s">
         <v>19</v>
@@ -10577,7 +10646,7 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B204" t="s">
         <v>13</v>
@@ -10590,7 +10659,7 @@
       </c>
       <c r="E204"/>
       <c r="F204" s="1" t="s">
-        <v>692</v>
+        <v>673</v>
       </c>
       <c r="G204" t="s">
         <v>19</v>
@@ -10607,7 +10676,7 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B205" t="s">
         <v>13</v>
@@ -10619,10 +10688,10 @@
         <v>25</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="G205" t="s">
         <v>19</v>
@@ -10639,7 +10708,7 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B206" t="s">
         <v>13</v>
@@ -10651,10 +10720,10 @@
         <v>25</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="G206" t="s">
         <v>19</v>
@@ -10671,7 +10740,7 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B207" t="s">
         <v>13</v>
@@ -10683,10 +10752,10 @@
         <v>25</v>
       </c>
       <c r="E207" t="s">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="G207" t="s">
         <v>19</v>
@@ -10703,7 +10772,7 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B208" t="s">
         <v>13</v>
@@ -10715,10 +10784,10 @@
         <v>25</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="G208" t="s">
         <v>19</v>
@@ -10735,7 +10804,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B209" t="s">
         <v>13</v>
@@ -10747,10 +10816,10 @@
         <v>25</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="G209" t="s">
         <v>19</v>
@@ -10767,7 +10836,7 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B210" t="s">
         <v>13</v>
@@ -10780,7 +10849,7 @@
       </c>
       <c r="E210"/>
       <c r="F210" s="1" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="G210" t="s">
         <v>19</v>
@@ -10797,7 +10866,7 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B211" t="s">
         <v>13</v>
@@ -10809,10 +10878,10 @@
         <v>25</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>705</v>
+        <v>686</v>
       </c>
       <c r="G211" t="s">
         <v>19</v>
@@ -10829,7 +10898,7 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B212" t="s">
         <v>13</v>
@@ -10841,10 +10910,10 @@
         <v>25</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="G212" t="s">
         <v>19</v>
@@ -10861,7 +10930,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B213" t="s">
         <v>13</v>
@@ -10873,10 +10942,10 @@
         <v>25</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="G213" t="s">
         <v>19</v>
@@ -10893,7 +10962,7 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B214" t="s">
         <v>13</v>
@@ -10906,7 +10975,7 @@
       </c>
       <c r="E214"/>
       <c r="F214" s="1" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="G214" t="s">
         <v>19</v>
@@ -10923,7 +10992,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B215" t="s">
         <v>13</v>
@@ -10935,10 +11004,10 @@
         <v>61</v>
       </c>
       <c r="E215" t="s">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="G215" t="s">
         <v>19</v>
@@ -10955,7 +11024,7 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B216" t="s">
         <v>13</v>
@@ -10967,10 +11036,10 @@
         <v>61</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="G216" t="s">
         <v>19</v>
@@ -10987,7 +11056,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B217" t="s">
         <v>13</v>
@@ -11000,7 +11069,7 @@
       </c>
       <c r="E217"/>
       <c r="F217" s="1" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="G217" t="s">
         <v>19</v>
@@ -11017,7 +11086,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B218" t="s">
         <v>13</v>
@@ -11029,10 +11098,10 @@
         <v>43</v>
       </c>
       <c r="E218" t="s">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="G218" t="s">
         <v>19</v>
@@ -11049,7 +11118,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B219" t="s">
         <v>13</v>
@@ -11061,10 +11130,10 @@
         <v>43</v>
       </c>
       <c r="E219" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="G219" t="s">
         <v>19</v>
@@ -11081,7 +11150,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B220" t="s">
         <v>13</v>
@@ -11090,13 +11159,13 @@
         <v>14</v>
       </c>
       <c r="D220" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="E220" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="G220" t="s">
         <v>19</v>
@@ -11113,7 +11182,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B221" t="s">
         <v>13</v>
@@ -11122,13 +11191,13 @@
         <v>14</v>
       </c>
       <c r="D221" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="E221" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="G221" t="s">
         <v>19</v>
@@ -11145,7 +11214,7 @@
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B222" t="s">
         <v>13</v>
@@ -11154,13 +11223,13 @@
         <v>14</v>
       </c>
       <c r="D222" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E222" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="F222" t="s">
-        <v>725</v>
+        <v>706</v>
       </c>
       <c r="G222" t="s">
         <v>19</v>
@@ -11177,7 +11246,7 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B223" t="s">
         <v>13</v>
@@ -11186,13 +11255,13 @@
         <v>14</v>
       </c>
       <c r="D223" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="E223" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="G223" t="s">
         <v>19</v>
@@ -11209,7 +11278,7 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B224" t="s">
         <v>13</v>
@@ -11218,13 +11287,13 @@
         <v>14</v>
       </c>
       <c r="D224" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="E224" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="G224" t="s">
         <v>19</v>
@@ -11241,7 +11310,7 @@
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B225" t="s">
         <v>13</v>
@@ -11250,13 +11319,13 @@
         <v>14</v>
       </c>
       <c r="D225" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="E225" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="G225" t="s">
         <v>19</v>
@@ -11273,7 +11342,7 @@
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B226" t="s">
         <v>13</v>
@@ -11282,13 +11351,13 @@
         <v>14</v>
       </c>
       <c r="D226" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="E226" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="G226" t="s">
         <v>19</v>
@@ -11305,7 +11374,7 @@
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B227" t="s">
         <v>13</v>
@@ -11314,13 +11383,13 @@
         <v>14</v>
       </c>
       <c r="D227" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="E227" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="G227" t="s">
         <v>19</v>
@@ -11337,7 +11406,7 @@
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B228" t="s">
         <v>13</v>
@@ -11346,13 +11415,13 @@
         <v>14</v>
       </c>
       <c r="D228" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E228" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="G228" t="s">
         <v>19</v>
@@ -11369,7 +11438,7 @@
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B229" t="s">
         <v>13</v>
@@ -11378,13 +11447,13 @@
         <v>14</v>
       </c>
       <c r="D229" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E229" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="G229" t="s">
         <v>19</v>
@@ -11401,7 +11470,7 @@
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B230" t="s">
         <v>13</v>
@@ -11410,11 +11479,11 @@
         <v>14</v>
       </c>
       <c r="D230" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E230"/>
       <c r="F230" s="1" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="G230" t="s">
         <v>19</v>
@@ -11431,7 +11500,7 @@
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B231" t="s">
         <v>13</v>
@@ -11440,11 +11509,11 @@
         <v>14</v>
       </c>
       <c r="D231" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E231"/>
       <c r="F231" s="1" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="G231" t="s">
         <v>19</v>
@@ -11461,7 +11530,7 @@
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B232" t="s">
         <v>13</v>
@@ -11470,13 +11539,13 @@
         <v>14</v>
       </c>
       <c r="D232" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E232" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="G232" t="s">
         <v>19</v>
@@ -11493,7 +11562,7 @@
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B233" t="s">
         <v>13</v>
@@ -11502,11 +11571,11 @@
         <v>14</v>
       </c>
       <c r="D233" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E233"/>
       <c r="F233" s="1" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="G233" t="s">
         <v>19</v>
@@ -11523,7 +11592,7 @@
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B234" t="s">
         <v>13</v>
@@ -11532,11 +11601,11 @@
         <v>14</v>
       </c>
       <c r="D234" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E234"/>
       <c r="F234" s="1" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="G234" t="s">
         <v>19</v>
@@ -11553,7 +11622,7 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B235" t="s">
         <v>13</v>
@@ -11562,11 +11631,11 @@
         <v>14</v>
       </c>
       <c r="D235" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E235"/>
       <c r="F235" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="G235" t="s">
         <v>19</v>
@@ -11583,7 +11652,7 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B236" t="s">
         <v>13</v>
@@ -11592,13 +11661,13 @@
         <v>14</v>
       </c>
       <c r="D236" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E236" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="G236" t="s">
         <v>19</v>
@@ -11615,7 +11684,7 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B237" t="s">
         <v>13</v>
@@ -11624,13 +11693,13 @@
         <v>14</v>
       </c>
       <c r="D237" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="E237" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="G237" t="s">
         <v>19</v>
@@ -11647,7 +11716,7 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B238" t="s">
         <v>13</v>
@@ -11656,11 +11725,11 @@
         <v>14</v>
       </c>
       <c r="D238" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="E238"/>
       <c r="F238" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="G238" t="s">
         <v>19</v>
@@ -11677,7 +11746,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B239" t="s">
         <v>13</v>
@@ -11686,13 +11755,13 @@
         <v>14</v>
       </c>
       <c r="D239" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="E239" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="F239" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="G239" t="s">
         <v>19</v>
@@ -11709,7 +11778,7 @@
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B240" t="s">
         <v>13</v>
@@ -11718,11 +11787,11 @@
         <v>14</v>
       </c>
       <c r="D240" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="E240"/>
       <c r="F240" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="G240" t="s">
         <v>19</v>
@@ -11739,7 +11808,7 @@
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B241" t="s">
         <v>13</v>
@@ -11748,13 +11817,13 @@
         <v>14</v>
       </c>
       <c r="D241" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E241" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="G241" t="s">
         <v>19</v>
@@ -11771,7 +11840,7 @@
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B242" t="s">
         <v>13</v>
@@ -11780,11 +11849,11 @@
         <v>14</v>
       </c>
       <c r="D242" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E242"/>
       <c r="F242" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="G242" t="s">
         <v>19</v>
@@ -11801,7 +11870,7 @@
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B243" t="s">
         <v>13</v>
@@ -11810,13 +11879,13 @@
         <v>14</v>
       </c>
       <c r="D243" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E243" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="F243" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="G243" t="s">
         <v>19</v>
@@ -11833,7 +11902,7 @@
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B244" t="s">
         <v>13</v>
@@ -11842,11 +11911,11 @@
         <v>14</v>
       </c>
       <c r="D244" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="E244"/>
       <c r="F244" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="G244" t="s">
         <v>19</v>
@@ -11863,7 +11932,7 @@
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B245" t="s">
         <v>13</v>
@@ -11872,11 +11941,11 @@
         <v>14</v>
       </c>
       <c r="D245" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E245"/>
       <c r="F245" t="s">
-        <v>765</v>
+        <v>746</v>
       </c>
       <c r="G245" t="s">
         <v>19</v>
@@ -11893,7 +11962,7 @@
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B246" t="s">
         <v>13</v>
@@ -11902,13 +11971,13 @@
         <v>14</v>
       </c>
       <c r="D246" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E246" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="F246" t="s">
-        <v>766</v>
+        <v>747</v>
       </c>
       <c r="G246" t="s">
         <v>19</v>
@@ -11925,7 +11994,7 @@
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B247" t="s">
         <v>13</v>
@@ -11934,13 +12003,13 @@
         <v>14</v>
       </c>
       <c r="D247" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E247" t="s">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="F247" t="s">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="G247" t="s">
         <v>19</v>
@@ -11957,7 +12026,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B248" t="s">
         <v>13</v>
@@ -11966,11 +12035,11 @@
         <v>14</v>
       </c>
       <c r="D248" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E248"/>
       <c r="F248" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
       <c r="G248" t="s">
         <v>19</v>
@@ -11987,7 +12056,7 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B249" t="s">
         <v>13</v>
@@ -11996,11 +12065,11 @@
         <v>14</v>
       </c>
       <c r="D249" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E249"/>
       <c r="F249" t="s">
-        <v>770</v>
+        <v>751</v>
       </c>
       <c r="G249" t="s">
         <v>19</v>
@@ -12017,7 +12086,7 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B250" t="s">
         <v>13</v>
@@ -12026,11 +12095,11 @@
         <v>14</v>
       </c>
       <c r="D250" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E250"/>
       <c r="F250" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="G250" t="s">
         <v>19</v>
@@ -12047,7 +12116,7 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B251" t="s">
         <v>13</v>
@@ -12056,11 +12125,11 @@
         <v>14</v>
       </c>
       <c r="D251" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E251"/>
       <c r="F251" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="G251" t="s">
         <v>19</v>
@@ -12077,7 +12146,7 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B252" t="s">
         <v>13</v>
@@ -12086,13 +12155,13 @@
         <v>14</v>
       </c>
       <c r="D252" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E252" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="G252" t="s">
         <v>19</v>
@@ -12109,7 +12178,7 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B253" t="s">
         <v>13</v>
@@ -12118,11 +12187,11 @@
         <v>14</v>
       </c>
       <c r="D253" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E253"/>
       <c r="F253" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="G253" t="s">
         <v>19</v>
@@ -12139,7 +12208,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B254" t="s">
         <v>13</v>
@@ -12148,13 +12217,13 @@
         <v>14</v>
       </c>
       <c r="D254" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="E254" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="G254" t="s">
         <v>19</v>
@@ -12171,7 +12240,7 @@
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B255" t="s">
         <v>13</v>
@@ -12180,11 +12249,11 @@
         <v>14</v>
       </c>
       <c r="D255" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="E255"/>
       <c r="F255" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
       <c r="G255" t="s">
         <v>19</v>
@@ -12201,7 +12270,7 @@
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B256" t="s">
         <v>13</v>
@@ -12210,11 +12279,11 @@
         <v>14</v>
       </c>
       <c r="D256" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E256"/>
       <c r="F256" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="G256" t="s">
         <v>19</v>
@@ -12231,7 +12300,7 @@
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B257" t="s">
         <v>13</v>
@@ -12240,13 +12309,13 @@
         <v>14</v>
       </c>
       <c r="D257" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="E257" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="G257" t="s">
         <v>19</v>
@@ -12263,7 +12332,7 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B258" t="s">
         <v>13</v>
@@ -12272,11 +12341,11 @@
         <v>14</v>
       </c>
       <c r="D258" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="E258"/>
       <c r="F258" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="G258" t="s">
         <v>19</v>
@@ -12293,7 +12362,7 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B259" t="s">
         <v>13</v>
@@ -12302,11 +12371,11 @@
         <v>14</v>
       </c>
       <c r="D259" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="E259"/>
       <c r="F259" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="G259" t="s">
         <v>19</v>
@@ -12323,7 +12392,7 @@
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B260" t="s">
         <v>13</v>
@@ -12332,11 +12401,11 @@
         <v>14</v>
       </c>
       <c r="D260" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="E260"/>
       <c r="F260" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="G260" t="s">
         <v>19</v>
@@ -12353,7 +12422,7 @@
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B261" t="s">
         <v>13</v>
@@ -12362,11 +12431,11 @@
         <v>14</v>
       </c>
       <c r="D261" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="E261"/>
       <c r="F261" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="G261" t="s">
         <v>19</v>
@@ -12383,7 +12452,7 @@
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B262" t="s">
         <v>13</v>
@@ -12392,13 +12461,13 @@
         <v>14</v>
       </c>
       <c r="D262" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="E262" t="s">
-        <v>920</v>
+        <v>901</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="G262" t="s">
         <v>19</v>
@@ -12415,7 +12484,7 @@
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B263" t="s">
         <v>13</v>
@@ -12424,13 +12493,13 @@
         <v>14</v>
       </c>
       <c r="D263" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="E263" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="F263" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="G263" t="s">
         <v>19</v>
@@ -12447,7 +12516,7 @@
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B264" t="s">
         <v>13</v>
@@ -12456,13 +12525,13 @@
         <v>14</v>
       </c>
       <c r="D264" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E264" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="F264" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="G264" t="s">
         <v>19</v>
@@ -12479,7 +12548,7 @@
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B265" t="s">
         <v>13</v>
@@ -12488,13 +12557,13 @@
         <v>14</v>
       </c>
       <c r="D265" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E265" t="s">
-        <v>792</v>
+        <v>773</v>
       </c>
       <c r="F265" t="s">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="G265" t="s">
         <v>19</v>
@@ -12511,7 +12580,7 @@
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B266" t="s">
         <v>13</v>
@@ -12520,11 +12589,11 @@
         <v>14</v>
       </c>
       <c r="D266" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="E266"/>
       <c r="F266" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="G266" t="s">
         <v>19</v>
@@ -12541,7 +12610,7 @@
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
@@ -12550,13 +12619,13 @@
         <v>14</v>
       </c>
       <c r="D267" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E267" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="F267" t="s">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="G267" t="s">
         <v>19</v>
@@ -12573,7 +12642,7 @@
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B268" t="s">
         <v>13</v>
@@ -12582,13 +12651,13 @@
         <v>14</v>
       </c>
       <c r="D268" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E268" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="F268" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="G268" t="s">
         <v>19</v>
@@ -12605,7 +12674,7 @@
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B269" t="s">
         <v>13</v>
@@ -12614,13 +12683,13 @@
         <v>14</v>
       </c>
       <c r="D269" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E269" t="s">
-        <v>800</v>
+        <v>781</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="G269" t="s">
         <v>19</v>
@@ -12637,7 +12706,7 @@
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B270" t="s">
         <v>13</v>
@@ -12646,13 +12715,13 @@
         <v>14</v>
       </c>
       <c r="D270" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E270" t="s">
-        <v>935</v>
+        <v>916</v>
       </c>
       <c r="F270" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="G270" t="s">
         <v>19</v>
@@ -12669,7 +12738,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B271" t="s">
         <v>13</v>
@@ -12678,13 +12747,13 @@
         <v>14</v>
       </c>
       <c r="D271" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E271" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="F271" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="G271" t="s">
         <v>19</v>
@@ -12701,7 +12770,7 @@
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B272" t="s">
         <v>13</v>
@@ -12710,11 +12779,11 @@
         <v>14</v>
       </c>
       <c r="D272" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E272"/>
       <c r="F272" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="G272" t="s">
         <v>19</v>
@@ -12731,7 +12800,7 @@
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B273" t="s">
         <v>13</v>
@@ -12740,13 +12809,13 @@
         <v>14</v>
       </c>
       <c r="D273" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E273" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="F273" t="s">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="G273" t="s">
         <v>19</v>
@@ -12763,7 +12832,7 @@
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B274" t="s">
         <v>13</v>
@@ -12772,13 +12841,13 @@
         <v>14</v>
       </c>
       <c r="D274" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E274" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="G274" t="s">
         <v>19</v>
@@ -12795,7 +12864,7 @@
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B275" t="s">
         <v>13</v>
@@ -12804,11 +12873,11 @@
         <v>14</v>
       </c>
       <c r="D275" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E275"/>
       <c r="F275" s="1" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="G275" t="s">
         <v>19</v>
@@ -12825,7 +12894,7 @@
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B276" t="s">
         <v>13</v>
@@ -12834,13 +12903,13 @@
         <v>14</v>
       </c>
       <c r="D276" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E276" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="G276" t="s">
         <v>19</v>
@@ -12857,7 +12926,7 @@
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B277" t="s">
         <v>13</v>
@@ -12866,13 +12935,13 @@
         <v>14</v>
       </c>
       <c r="D277" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E277" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="G277" t="s">
         <v>19</v>
@@ -12889,7 +12958,7 @@
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B278" t="s">
         <v>13</v>
@@ -12898,11 +12967,11 @@
         <v>14</v>
       </c>
       <c r="D278" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E278"/>
       <c r="F278" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="G278" t="s">
         <v>19</v>
@@ -12919,7 +12988,7 @@
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B279" t="s">
         <v>13</v>
@@ -12928,13 +12997,13 @@
         <v>14</v>
       </c>
       <c r="D279" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E279" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="F279" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="G279" t="s">
         <v>19</v>
@@ -12951,7 +13020,7 @@
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B280" t="s">
         <v>13</v>
@@ -12960,13 +13029,13 @@
         <v>14</v>
       </c>
       <c r="D280" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E280" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>921</v>
+        <v>902</v>
       </c>
       <c r="G280" t="s">
         <v>19</v>
@@ -12983,7 +13052,7 @@
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B281" t="s">
         <v>13</v>
@@ -12992,11 +13061,11 @@
         <v>14</v>
       </c>
       <c r="D281" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E281"/>
       <c r="F281" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="G281" t="s">
         <v>19</v>
@@ -13013,7 +13082,7 @@
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B282" t="s">
         <v>13</v>
@@ -13022,13 +13091,13 @@
         <v>14</v>
       </c>
       <c r="D282" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E282" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="F282" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="G282" t="s">
         <v>19</v>
@@ -13045,7 +13114,7 @@
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B283" t="s">
         <v>13</v>
@@ -13054,13 +13123,13 @@
         <v>14</v>
       </c>
       <c r="D283" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E283" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="G283" t="s">
         <v>19</v>
@@ -13077,7 +13146,7 @@
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B284" t="s">
         <v>13</v>
@@ -13086,13 +13155,13 @@
         <v>14</v>
       </c>
       <c r="D284" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E284" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="G284" t="s">
         <v>19</v>
@@ -13109,7 +13178,7 @@
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B285" t="s">
         <v>13</v>
@@ -13118,11 +13187,11 @@
         <v>14</v>
       </c>
       <c r="D285" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E285"/>
       <c r="F285" s="1" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="G285" t="s">
         <v>19</v>
@@ -13139,7 +13208,7 @@
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B286" t="s">
         <v>13</v>
@@ -13148,13 +13217,13 @@
         <v>14</v>
       </c>
       <c r="D286" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E286" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="G286" t="s">
         <v>19</v>
@@ -13171,7 +13240,7 @@
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B287" t="s">
         <v>13</v>
@@ -13180,11 +13249,11 @@
         <v>14</v>
       </c>
       <c r="D287" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E287"/>
       <c r="F287" s="1" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
       <c r="G287" t="s">
         <v>19</v>
@@ -13201,7 +13270,7 @@
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B288" t="s">
         <v>13</v>
@@ -13210,13 +13279,13 @@
         <v>14</v>
       </c>
       <c r="D288" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E288" t="s">
-        <v>923</v>
+        <v>904</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>922</v>
+        <v>903</v>
       </c>
       <c r="G288" t="s">
         <v>19</v>
@@ -13233,7 +13302,7 @@
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B289" t="s">
         <v>13</v>
@@ -13242,11 +13311,11 @@
         <v>14</v>
       </c>
       <c r="D289" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E289"/>
       <c r="F289" t="s">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="G289" t="s">
         <v>19</v>
@@ -13263,7 +13332,7 @@
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B290" t="s">
         <v>13</v>
@@ -13272,13 +13341,13 @@
         <v>14</v>
       </c>
       <c r="D290" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E290" t="s">
-        <v>829</v>
+        <v>810</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="G290" t="s">
         <v>19</v>
@@ -13295,7 +13364,7 @@
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B291" t="s">
         <v>13</v>
@@ -13304,13 +13373,13 @@
         <v>14</v>
       </c>
       <c r="D291" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E291" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="F291" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="G291" t="s">
         <v>19</v>
@@ -13327,7 +13396,7 @@
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B292" t="s">
         <v>13</v>
@@ -13336,13 +13405,13 @@
         <v>14</v>
       </c>
       <c r="D292" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E292" t="s">
-        <v>932</v>
+        <v>913</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>933</v>
+        <v>914</v>
       </c>
       <c r="G292" t="s">
         <v>19</v>
@@ -13359,7 +13428,7 @@
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B293" t="s">
         <v>13</v>
@@ -13368,11 +13437,11 @@
         <v>14</v>
       </c>
       <c r="D293" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E293"/>
       <c r="F293" t="s">
-        <v>833</v>
+        <v>814</v>
       </c>
       <c r="G293" t="s">
         <v>19</v>
@@ -13389,7 +13458,7 @@
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B294" t="s">
         <v>13</v>
@@ -13398,13 +13467,13 @@
         <v>14</v>
       </c>
       <c r="D294" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E294" t="s">
-        <v>927</v>
+        <v>908</v>
       </c>
       <c r="F294" t="s">
-        <v>834</v>
+        <v>815</v>
       </c>
       <c r="G294" t="s">
         <v>19</v>
@@ -13421,7 +13490,7 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B295" t="s">
         <v>13</v>
@@ -13430,13 +13499,13 @@
         <v>14</v>
       </c>
       <c r="D295" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E295" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="G295" t="s">
         <v>19</v>
@@ -13453,7 +13522,7 @@
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B296" t="s">
         <v>13</v>
@@ -13462,13 +13531,13 @@
         <v>14</v>
       </c>
       <c r="D296" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E296" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="F296" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="G296" t="s">
         <v>19</v>
@@ -13485,7 +13554,7 @@
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B297" t="s">
         <v>13</v>
@@ -13494,11 +13563,11 @@
         <v>14</v>
       </c>
       <c r="D297" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E297"/>
       <c r="F297" s="1" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="G297" t="s">
         <v>19</v>
@@ -13515,7 +13584,7 @@
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B298" t="s">
         <v>13</v>
@@ -13524,13 +13593,13 @@
         <v>14</v>
       </c>
       <c r="D298" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E298" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>836</v>
+        <v>817</v>
       </c>
       <c r="G298" t="s">
         <v>19</v>
@@ -13547,7 +13616,7 @@
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B299" t="s">
         <v>13</v>
@@ -13556,13 +13625,13 @@
         <v>14</v>
       </c>
       <c r="D299" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E299" t="s">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>838</v>
+        <v>819</v>
       </c>
       <c r="G299" t="s">
         <v>19</v>
@@ -13579,7 +13648,7 @@
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B300" t="s">
         <v>13</v>
@@ -13588,13 +13657,13 @@
         <v>14</v>
       </c>
       <c r="D300" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E300" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="G300" t="s">
         <v>19</v>
@@ -13611,7 +13680,7 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B301" t="s">
         <v>13</v>
@@ -13620,13 +13689,13 @@
         <v>14</v>
       </c>
       <c r="D301" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E301" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>934</v>
+        <v>915</v>
       </c>
       <c r="G301" t="s">
         <v>19</v>
@@ -13643,7 +13712,7 @@
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B302" t="s">
         <v>13</v>
@@ -13652,13 +13721,13 @@
         <v>14</v>
       </c>
       <c r="D302" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E302" t="s">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>843</v>
+        <v>824</v>
       </c>
       <c r="G302" t="s">
         <v>19</v>
@@ -13675,7 +13744,7 @@
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B303" t="s">
         <v>13</v>
@@ -13684,11 +13753,11 @@
         <v>14</v>
       </c>
       <c r="D303" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E303"/>
       <c r="F303" s="1" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="G303" t="s">
         <v>19</v>
@@ -13705,7 +13774,7 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B304" t="s">
         <v>13</v>
@@ -13714,13 +13783,13 @@
         <v>14</v>
       </c>
       <c r="D304" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="E304" t="s">
-        <v>845</v>
+        <v>826</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>846</v>
+        <v>827</v>
       </c>
       <c r="G304" t="s">
         <v>19</v>
@@ -13737,7 +13806,7 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B305" t="s">
         <v>13</v>
@@ -13746,11 +13815,11 @@
         <v>14</v>
       </c>
       <c r="D305" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="E305"/>
       <c r="F305" s="1" t="s">
-        <v>847</v>
+        <v>828</v>
       </c>
       <c r="G305" t="s">
         <v>19</v>
@@ -13767,7 +13836,7 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B306" t="s">
         <v>13</v>
@@ -13776,13 +13845,13 @@
         <v>14</v>
       </c>
       <c r="D306" t="s">
-        <v>848</v>
+        <v>829</v>
       </c>
       <c r="E306" t="s">
-        <v>849</v>
+        <v>830</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>850</v>
+        <v>831</v>
       </c>
       <c r="G306" t="s">
         <v>19</v>
@@ -13799,7 +13868,7 @@
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B307" t="s">
         <v>13</v>
@@ -13808,11 +13877,11 @@
         <v>14</v>
       </c>
       <c r="D307" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="E307"/>
       <c r="F307" t="s">
-        <v>851</v>
+        <v>832</v>
       </c>
       <c r="G307" t="s">
         <v>19</v>
@@ -13829,7 +13898,7 @@
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B308" t="s">
         <v>13</v>
@@ -13838,11 +13907,11 @@
         <v>14</v>
       </c>
       <c r="D308" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E308"/>
       <c r="F308" t="s">
-        <v>852</v>
+        <v>833</v>
       </c>
       <c r="G308" t="s">
         <v>19</v>
@@ -13859,7 +13928,7 @@
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B309" t="s">
         <v>13</v>
@@ -13868,11 +13937,11 @@
         <v>14</v>
       </c>
       <c r="D309" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E309"/>
       <c r="F309" t="s">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="G309" t="s">
         <v>19</v>
@@ -13889,7 +13958,7 @@
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B310" t="s">
         <v>13</v>
@@ -13898,13 +13967,13 @@
         <v>14</v>
       </c>
       <c r="D310" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E310" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>917</v>
+        <v>898</v>
       </c>
       <c r="G310" t="s">
         <v>19</v>
@@ -13921,7 +13990,7 @@
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B311" t="s">
         <v>13</v>
@@ -13930,11 +13999,11 @@
         <v>14</v>
       </c>
       <c r="D311" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E311"/>
       <c r="F311" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="G311" t="s">
         <v>19</v>
@@ -13951,7 +14020,7 @@
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B312" t="s">
         <v>13</v>
@@ -13960,13 +14029,13 @@
         <v>14</v>
       </c>
       <c r="D312" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E312" t="s">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="F312" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
       <c r="G312" t="s">
         <v>19</v>
@@ -13983,7 +14052,7 @@
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B313" t="s">
         <v>13</v>
@@ -13992,11 +14061,11 @@
         <v>14</v>
       </c>
       <c r="D313" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E313"/>
       <c r="F313" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="G313" t="s">
         <v>19</v>
@@ -14013,7 +14082,7 @@
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B314" t="s">
         <v>13</v>
@@ -14022,11 +14091,11 @@
         <v>14</v>
       </c>
       <c r="D314" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E314"/>
       <c r="F314" s="1" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="G314" t="s">
         <v>19</v>
@@ -14043,7 +14112,7 @@
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B315" t="s">
         <v>13</v>
@@ -14052,13 +14121,13 @@
         <v>14</v>
       </c>
       <c r="D315" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E315" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="G315" t="s">
         <v>19</v>
@@ -14075,7 +14144,7 @@
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B316" t="s">
         <v>13</v>
@@ -14084,11 +14153,11 @@
         <v>14</v>
       </c>
       <c r="D316" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="E316"/>
       <c r="F316" s="1" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="G316" t="s">
         <v>19</v>
@@ -14105,7 +14174,7 @@
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B317" t="s">
         <v>13</v>
@@ -14114,11 +14183,11 @@
         <v>14</v>
       </c>
       <c r="D317" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="E317"/>
       <c r="F317" s="1" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="G317" t="s">
         <v>19</v>
@@ -14135,7 +14204,7 @@
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B318" t="s">
         <v>13</v>
@@ -14144,11 +14213,11 @@
         <v>14</v>
       </c>
       <c r="D318" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E318"/>
       <c r="F318" s="1" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="G318" t="s">
         <v>19</v>
@@ -14165,7 +14234,7 @@
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B319" t="s">
         <v>13</v>
@@ -14174,11 +14243,11 @@
         <v>14</v>
       </c>
       <c r="D319" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E319"/>
       <c r="F319" s="1" t="s">
-        <v>865</v>
+        <v>846</v>
       </c>
       <c r="G319" t="s">
         <v>19</v>
@@ -14195,7 +14264,7 @@
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B320" t="s">
         <v>13</v>
@@ -14204,13 +14273,13 @@
         <v>14</v>
       </c>
       <c r="D320" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E320" t="s">
-        <v>866</v>
+        <v>847</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>867</v>
+        <v>848</v>
       </c>
       <c r="G320" t="s">
         <v>19</v>
@@ -14227,7 +14296,7 @@
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B321" t="s">
         <v>13</v>
@@ -14236,13 +14305,13 @@
         <v>14</v>
       </c>
       <c r="D321" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="E321" t="s">
-        <v>868</v>
+        <v>849</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>869</v>
+        <v>850</v>
       </c>
       <c r="G321" t="s">
         <v>19</v>
@@ -14259,7 +14328,7 @@
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B322" t="s">
         <v>13</v>
@@ -14268,13 +14337,13 @@
         <v>14</v>
       </c>
       <c r="D322" t="s">
-        <v>870</v>
+        <v>851</v>
       </c>
       <c r="E322" t="s">
-        <v>871</v>
+        <v>852</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>872</v>
+        <v>853</v>
       </c>
       <c r="G322" t="s">
         <v>19</v>
@@ -14291,7 +14360,7 @@
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B323" t="s">
         <v>13</v>
@@ -14300,11 +14369,11 @@
         <v>14</v>
       </c>
       <c r="D323" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E323"/>
       <c r="F323" s="1" t="s">
-        <v>873</v>
+        <v>854</v>
       </c>
       <c r="G323" t="s">
         <v>19</v>
@@ -14321,7 +14390,7 @@
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B324" t="s">
         <v>13</v>
@@ -14330,13 +14399,13 @@
         <v>14</v>
       </c>
       <c r="D324" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="E324" t="s">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>875</v>
+        <v>856</v>
       </c>
       <c r="G324" t="s">
         <v>19</v>
@@ -14353,7 +14422,7 @@
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B325" t="s">
         <v>13</v>
@@ -14362,11 +14431,11 @@
         <v>14</v>
       </c>
       <c r="D325" t="s">
-        <v>651</v>
+        <v>632</v>
       </c>
       <c r="E325"/>
       <c r="F325" s="1" t="s">
-        <v>876</v>
+        <v>857</v>
       </c>
       <c r="G325" t="s">
         <v>19</v>
@@ -14383,7 +14452,7 @@
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B326" t="s">
         <v>13</v>
@@ -14392,11 +14461,11 @@
         <v>14</v>
       </c>
       <c r="D326" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="E326"/>
       <c r="F326" s="1" t="s">
-        <v>878</v>
+        <v>859</v>
       </c>
       <c r="G326" t="s">
         <v>19</v>
@@ -14413,7 +14482,7 @@
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B327" t="s">
         <v>13</v>
@@ -14422,13 +14491,13 @@
         <v>14</v>
       </c>
       <c r="D327" t="s">
-        <v>879</v>
+        <v>860</v>
       </c>
       <c r="E327" t="s">
-        <v>880</v>
+        <v>861</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>881</v>
+        <v>862</v>
       </c>
       <c r="G327" t="s">
         <v>19</v>
@@ -14445,7 +14514,7 @@
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B328" t="s">
         <v>13</v>
@@ -14454,13 +14523,13 @@
         <v>14</v>
       </c>
       <c r="D328" t="s">
-        <v>882</v>
+        <v>863</v>
       </c>
       <c r="E328" t="s">
-        <v>883</v>
+        <v>864</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>884</v>
+        <v>865</v>
       </c>
       <c r="G328" t="s">
         <v>19</v>
@@ -14477,7 +14546,7 @@
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B329" t="s">
         <v>13</v>
@@ -14486,11 +14555,11 @@
         <v>14</v>
       </c>
       <c r="D329" t="s">
-        <v>885</v>
+        <v>866</v>
       </c>
       <c r="E329"/>
       <c r="F329" s="1" t="s">
-        <v>886</v>
+        <v>867</v>
       </c>
       <c r="G329" t="s">
         <v>19</v>
@@ -14507,7 +14576,7 @@
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B330" t="s">
         <v>13</v>
@@ -14516,13 +14585,13 @@
         <v>14</v>
       </c>
       <c r="D330" t="s">
-        <v>887</v>
+        <v>868</v>
       </c>
       <c r="E330" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="G330" t="s">
         <v>19</v>
@@ -14539,7 +14608,7 @@
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B331" t="s">
         <v>13</v>
@@ -14548,13 +14617,13 @@
         <v>14</v>
       </c>
       <c r="D331" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="E331" t="s">
-        <v>891</v>
+        <v>872</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>892</v>
+        <v>873</v>
       </c>
       <c r="G331" t="s">
         <v>19</v>
@@ -14571,7 +14640,7 @@
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B332" t="s">
         <v>13</v>
@@ -14580,13 +14649,13 @@
         <v>14</v>
       </c>
       <c r="D332" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="E332" t="s">
-        <v>893</v>
+        <v>874</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>894</v>
+        <v>875</v>
       </c>
       <c r="G332" t="s">
         <v>19</v>
@@ -14603,7 +14672,7 @@
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B333" t="s">
         <v>13</v>
@@ -14612,11 +14681,11 @@
         <v>14</v>
       </c>
       <c r="D333" t="s">
-        <v>895</v>
+        <v>876</v>
       </c>
       <c r="E333"/>
       <c r="F333" s="1" t="s">
-        <v>896</v>
+        <v>877</v>
       </c>
       <c r="G333" t="s">
         <v>19</v>
@@ -14633,7 +14702,7 @@
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B334" t="s">
         <v>13</v>
@@ -14642,13 +14711,13 @@
         <v>14</v>
       </c>
       <c r="D334" t="s">
-        <v>897</v>
+        <v>878</v>
       </c>
       <c r="E334" t="s">
-        <v>898</v>
+        <v>879</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="G334" t="s">
         <v>19</v>
@@ -14665,7 +14734,7 @@
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B335" t="s">
         <v>13</v>
@@ -14674,13 +14743,13 @@
         <v>14</v>
       </c>
       <c r="D335" t="s">
-        <v>900</v>
+        <v>881</v>
       </c>
       <c r="E335" t="s">
-        <v>901</v>
+        <v>882</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="G335" t="s">
         <v>19</v>
@@ -14697,7 +14766,7 @@
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B336" t="s">
         <v>13</v>
@@ -14706,13 +14775,13 @@
         <v>14</v>
       </c>
       <c r="D336" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E336" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>904</v>
+        <v>885</v>
       </c>
       <c r="G336" t="s">
         <v>19</v>
@@ -14729,7 +14798,7 @@
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B337" t="s">
         <v>13</v>
@@ -14738,13 +14807,13 @@
         <v>14</v>
       </c>
       <c r="D337" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E337" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="G337" t="s">
         <v>19</v>
@@ -14761,7 +14830,7 @@
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B338" t="s">
         <v>13</v>
@@ -14770,13 +14839,13 @@
         <v>14</v>
       </c>
       <c r="D338" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E338" t="s">
-        <v>907</v>
+        <v>888</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="G338" t="s">
         <v>19</v>
@@ -14793,7 +14862,7 @@
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B339" t="s">
         <v>13</v>
@@ -14802,13 +14871,13 @@
         <v>14</v>
       </c>
       <c r="D339" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E339" t="s">
-        <v>909</v>
+        <v>890</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>910</v>
+        <v>891</v>
       </c>
       <c r="G339" t="s">
         <v>19</v>
@@ -14825,7 +14894,7 @@
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B340" t="s">
         <v>13</v>
@@ -14834,13 +14903,13 @@
         <v>14</v>
       </c>
       <c r="D340" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E340" t="s">
-        <v>911</v>
+        <v>892</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="G340" t="s">
         <v>19</v>
@@ -14857,7 +14926,7 @@
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B341" t="s">
         <v>13</v>
@@ -14866,13 +14935,13 @@
         <v>14</v>
       </c>
       <c r="D341" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="E341" t="s">
-        <v>913</v>
+        <v>894</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>914</v>
+        <v>895</v>
       </c>
       <c r="G341" t="s">
         <v>19</v>
@@ -14889,7 +14958,7 @@
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="B342" t="s">
         <v>13</v>
@@ -14898,13 +14967,13 @@
         <v>14</v>
       </c>
       <c r="D342" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E342" t="s">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="F342" t="s">
-        <v>916</v>
+        <v>897</v>
       </c>
       <c r="G342" t="s">
         <v>19</v>
@@ -15027,6 +15096,25 @@
     <hyperlink ref="F275" r:id="rId103" xr:uid="{C9260396-C81F-43AE-8140-AF36972DFE57}"/>
     <hyperlink ref="H163" r:id="rId104" xr:uid="{5BFBA6A0-6CB8-47F6-A1B2-D6696E0A3326}"/>
     <hyperlink ref="J122" r:id="rId105" xr:uid="{91B5C5CC-D039-4D6D-A53C-96732530C258}"/>
+    <hyperlink ref="H167" r:id="rId106" xr:uid="{1DEA3C89-0CBF-46F2-8B94-1CF97CD0C6A0}"/>
+    <hyperlink ref="H166" r:id="rId107" xr:uid="{E98FDB78-BB91-41B9-9D9A-478919648B01}"/>
+    <hyperlink ref="J166" r:id="rId108" xr:uid="{A9DF82D0-0414-465D-ADD1-39268F3D8277}"/>
+    <hyperlink ref="H160" r:id="rId109" xr:uid="{674B34E5-928A-4C2F-A2A0-3698CD65C0B9}"/>
+    <hyperlink ref="H156" r:id="rId110" xr:uid="{CA766513-D9A3-4AE6-90B3-674B5AE28ED7}"/>
+    <hyperlink ref="J150" r:id="rId111" xr:uid="{F98A2376-6F1E-44E3-8D46-2839A85B9D6E}"/>
+    <hyperlink ref="J104" r:id="rId112" xr:uid="{846CDFF4-2DAF-4853-A638-CCBBD43BC227}"/>
+    <hyperlink ref="H43" r:id="rId113" xr:uid="{BE798B49-ECB1-4FE2-A61E-7035BB12CDB3}"/>
+    <hyperlink ref="H24" r:id="rId114" xr:uid="{B7C3AC12-603F-4243-9758-FDA680AC2F86}"/>
+    <hyperlink ref="J24" r:id="rId115" xr:uid="{5310559D-D8BE-4E53-B841-A9960B388D91}"/>
+    <hyperlink ref="H16" r:id="rId116" xr:uid="{B1A75A46-5069-451C-9A68-8ED8187EF9F8}"/>
+    <hyperlink ref="H42" r:id="rId117" xr:uid="{129BF063-C61A-4E08-BAF4-55C8B60CACC1}"/>
+    <hyperlink ref="F90" r:id="rId118" xr:uid="{180905F7-91E4-4386-8751-5999B52F3931}"/>
+    <hyperlink ref="H90" r:id="rId119" xr:uid="{10734566-FDC4-4981-A087-EB61F36248C1}"/>
+    <hyperlink ref="J90" r:id="rId120" xr:uid="{713D435B-77F8-4610-A84A-8C291D3638AB}"/>
+    <hyperlink ref="F95" r:id="rId121" xr:uid="{DE4689F7-ABD8-4EF8-8E92-3FD8BB1BAC19}"/>
+    <hyperlink ref="J95" r:id="rId122" xr:uid="{88D346BF-DD10-4CE7-A12D-07F3955A5105}"/>
+    <hyperlink ref="H95" r:id="rId123" xr:uid="{C4025397-2E5E-4A44-9264-51E3F5D4E892}"/>
+    <hyperlink ref="H104" r:id="rId124" xr:uid="{C40B8DDE-14F9-420E-AAB9-72C840751240}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/collected-data.xlsx
+++ b/collected-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-26.04\home\leo\OS-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DFC056-8FF7-445B-8CE6-484A5082A82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD397F4-2E78-442B-A31A-83A72B33B1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3083" uniqueCount="952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="954">
   <si>
     <t>年份</t>
   </si>
@@ -2813,10 +2813,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/hzc1998/oskernel2021-xbook2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://gitlab.eduxiji.net/lightenos/oskernel2025-lightenos</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2829,10 +2825,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>已私密/删库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://gitlab.eduxiji.net/potato-kernal/cy-os</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2926,6 +2918,22 @@
   </si>
   <si>
     <t>失效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitee.com/hzc1998/xbook2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gitee版最新，github版： https://github.com/hzcx998/xbook2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/os-contest-2021-kernel-final-scene/potato-kernal-cy-os</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">github版  https://github.com/Godones/Alien  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3901,7 +3909,7 @@
         <v>17</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>63</v>
@@ -3910,7 +3918,9 @@
       <c r="K16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3" t="s">
+        <v>953</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
@@ -4014,7 +4024,7 @@
         <v>77</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>79</v>
@@ -4187,19 +4197,19 @@
         <v>17</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>935</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>937</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -4839,16 +4849,16 @@
         <v>19</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -4875,7 +4885,7 @@
         <v>17</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>19</v>
@@ -6584,25 +6594,25 @@
         <v>314</v>
       </c>
       <c r="E90" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="I90" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>945</v>
-      </c>
       <c r="K90" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
@@ -6773,19 +6783,19 @@
         <v>335</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>948</v>
-      </c>
       <c r="I95" s="3" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>19</v>
@@ -7105,16 +7115,16 @@
         <v>17</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
@@ -7764,7 +7774,7 @@
         <v>431</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="J122" s="1" t="s">
         <v>922</v>
@@ -8773,7 +8783,7 @@
         <v>17</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>19</v>
@@ -8985,10 +8995,10 @@
         <v>19</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="J156" s="3" t="s">
         <v>543</v>
@@ -9127,14 +9137,16 @@
         <v>17</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J160" s="3"/>
+      <c r="J160" s="1" t="s">
+        <v>952</v>
+      </c>
       <c r="K160" s="3" t="s">
-        <v>17</v>
+        <v>925</v>
       </c>
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
@@ -9339,13 +9351,13 @@
         <v>17</v>
       </c>
       <c r="H166" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="J166" s="1" t="s">
         <v>924</v>
-      </c>
-      <c r="I166" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>925</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>19</v>
@@ -9375,16 +9387,18 @@
         <v>17</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J167" s="3"/>
       <c r="K167" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L167" s="3"/>
+      <c r="L167" s="3" t="s">
+        <v>951</v>
+      </c>
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
     </row>
@@ -15115,6 +15129,7 @@
     <hyperlink ref="J95" r:id="rId122" xr:uid="{88D346BF-DD10-4CE7-A12D-07F3955A5105}"/>
     <hyperlink ref="H95" r:id="rId123" xr:uid="{C4025397-2E5E-4A44-9264-51E3F5D4E892}"/>
     <hyperlink ref="H104" r:id="rId124" xr:uid="{C40B8DDE-14F9-420E-AAB9-72C840751240}"/>
+    <hyperlink ref="J160" r:id="rId125" xr:uid="{519864A7-D732-4BDC-9E57-FD28948FFEE2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/collected-data.xlsx
+++ b/collected-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-26.04\home\leo\OS-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD397F4-2E78-442B-A31A-83A72B33B1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E655A06D-A549-4DEB-B9BA-86884517BADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2548,9 +2548,6 @@
     <t>夺金入场</t>
   </si>
   <si>
-    <t>https://gitlab.eduxiji.net/educg-group-43501-3132633/T202610574999863-772</t>
-  </si>
-  <si>
     <t>https://gitlab.eduxiji.net/educg-group-43501-3132633/T202610574999903-2691</t>
   </si>
   <si>
@@ -2934,6 +2931,10 @@
   </si>
   <si>
     <t xml:space="preserve">github版  https://github.com/Godones/Alien  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://gitlab.eduxiji.net/educg-group-43501-3132633/T202610574999863-772</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3909,7 +3910,7 @@
         <v>17</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>63</v>
@@ -3919,7 +3920,7 @@
         <v>17</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -4024,7 +4025,7 @@
         <v>77</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>79</v>
@@ -4197,19 +4198,19 @@
         <v>17</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>934</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>935</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -4849,16 +4850,16 @@
         <v>19</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>938</v>
-      </c>
       <c r="K42" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -4885,7 +4886,7 @@
         <v>17</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>19</v>
@@ -6594,25 +6595,25 @@
         <v>314</v>
       </c>
       <c r="E90" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="G90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H90" s="1" t="s">
+      <c r="I90" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>943</v>
-      </c>
       <c r="K90" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
@@ -6783,19 +6784,19 @@
         <v>335</v>
       </c>
       <c r="F95" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>944</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>945</v>
       </c>
       <c r="K95" s="3" t="s">
         <v>19</v>
@@ -7115,16 +7116,16 @@
         <v>17</v>
       </c>
       <c r="H104" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="K104" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="K104" s="3" t="s">
-        <v>949</v>
       </c>
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
@@ -7774,10 +7775,10 @@
         <v>431</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K122" s="3" t="s">
         <v>19</v>
@@ -7985,7 +7986,7 @@
         <v>17</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>78</v>
@@ -8783,7 +8784,7 @@
         <v>17</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>19</v>
@@ -8995,10 +8996,10 @@
         <v>19</v>
       </c>
       <c r="H156" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="I156" s="3" t="s">
         <v>927</v>
-      </c>
-      <c r="I156" s="3" t="s">
-        <v>928</v>
       </c>
       <c r="J156" s="3" t="s">
         <v>543</v>
@@ -9137,16 +9138,16 @@
         <v>17</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>63</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="K160" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
@@ -9245,7 +9246,7 @@
         <v>17</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>19</v>
@@ -9351,13 +9352,13 @@
         <v>17</v>
       </c>
       <c r="H166" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="J166" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="I166" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>924</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>19</v>
@@ -9387,17 +9388,17 @@
         <v>17</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J167" s="3"/>
       <c r="K167" s="3" t="s">
         <v>17</v>
       </c>
       <c r="L167" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
@@ -11681,7 +11682,7 @@
         <v>730</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G236" t="s">
         <v>19</v>
@@ -11988,7 +11989,7 @@
         <v>170</v>
       </c>
       <c r="E246" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F246" t="s">
         <v>747</v>
@@ -12234,10 +12235,10 @@
         <v>757</v>
       </c>
       <c r="E254" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G254" t="s">
         <v>19</v>
@@ -12326,10 +12327,10 @@
         <v>761</v>
       </c>
       <c r="E257" t="s">
+        <v>909</v>
+      </c>
+      <c r="F257" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="F257" s="1" t="s">
-        <v>911</v>
       </c>
       <c r="G257" t="s">
         <v>19</v>
@@ -12478,7 +12479,7 @@
         <v>531</v>
       </c>
       <c r="E262" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>768</v>
@@ -12732,7 +12733,7 @@
         <v>418</v>
       </c>
       <c r="E270" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F270" t="s">
         <v>783</v>
@@ -12891,7 +12892,7 @@
       </c>
       <c r="E275"/>
       <c r="F275" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G275" t="s">
         <v>19</v>
@@ -13049,7 +13050,7 @@
         <v>797</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G280" t="s">
         <v>19</v>
@@ -13296,10 +13297,10 @@
         <v>418</v>
       </c>
       <c r="E288" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G288" t="s">
         <v>19</v>
@@ -13422,10 +13423,10 @@
         <v>418</v>
       </c>
       <c r="E292" t="s">
+        <v>912</v>
+      </c>
+      <c r="F292" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>914</v>
       </c>
       <c r="G292" t="s">
         <v>19</v>
@@ -13484,7 +13485,7 @@
         <v>418</v>
       </c>
       <c r="E294" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F294" t="s">
         <v>815</v>
@@ -13516,10 +13517,10 @@
         <v>418</v>
       </c>
       <c r="E295" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G295" t="s">
         <v>19</v>
@@ -13548,7 +13549,7 @@
         <v>418</v>
       </c>
       <c r="E296" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F296" t="s">
         <v>816</v>
@@ -13581,7 +13582,7 @@
       </c>
       <c r="E297"/>
       <c r="F297" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G297" t="s">
         <v>19</v>
@@ -13709,7 +13710,7 @@
         <v>822</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G301" t="s">
         <v>19</v>
@@ -13987,7 +13988,7 @@
         <v>836</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G310" t="s">
         <v>19</v>
@@ -14046,7 +14047,7 @@
         <v>835</v>
       </c>
       <c r="E312" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F312" t="s">
         <v>838</v>
@@ -14141,7 +14142,7 @@
         <v>841</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>842</v>
+        <v>953</v>
       </c>
       <c r="G315" t="s">
         <v>19</v>
@@ -14171,7 +14172,7 @@
       </c>
       <c r="E316"/>
       <c r="F316" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G316" t="s">
         <v>19</v>
@@ -14201,7 +14202,7 @@
       </c>
       <c r="E317"/>
       <c r="F317" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G317" t="s">
         <v>19</v>
@@ -14231,7 +14232,7 @@
       </c>
       <c r="E318"/>
       <c r="F318" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G318" t="s">
         <v>19</v>
@@ -14261,7 +14262,7 @@
       </c>
       <c r="E319"/>
       <c r="F319" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G319" t="s">
         <v>19</v>
@@ -14290,10 +14291,10 @@
         <v>69</v>
       </c>
       <c r="E320" t="s">
+        <v>846</v>
+      </c>
+      <c r="F320" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="F320" s="1" t="s">
-        <v>848</v>
       </c>
       <c r="G320" t="s">
         <v>19</v>
@@ -14322,10 +14323,10 @@
         <v>574</v>
       </c>
       <c r="E321" t="s">
+        <v>848</v>
+      </c>
+      <c r="F321" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="F321" s="1" t="s">
-        <v>850</v>
       </c>
       <c r="G321" t="s">
         <v>19</v>
@@ -14351,13 +14352,13 @@
         <v>14</v>
       </c>
       <c r="D322" t="s">
+        <v>850</v>
+      </c>
+      <c r="E322" t="s">
         <v>851</v>
       </c>
-      <c r="E322" t="s">
+      <c r="F322" s="1" t="s">
         <v>852</v>
-      </c>
-      <c r="F322" s="1" t="s">
-        <v>853</v>
       </c>
       <c r="G322" t="s">
         <v>19</v>
@@ -14387,7 +14388,7 @@
       </c>
       <c r="E323"/>
       <c r="F323" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G323" t="s">
         <v>19</v>
@@ -14416,10 +14417,10 @@
         <v>456</v>
       </c>
       <c r="E324" t="s">
+        <v>854</v>
+      </c>
+      <c r="F324" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="F324" s="1" t="s">
-        <v>856</v>
       </c>
       <c r="G324" t="s">
         <v>19</v>
@@ -14449,7 +14450,7 @@
       </c>
       <c r="E325"/>
       <c r="F325" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G325" t="s">
         <v>19</v>
@@ -14475,11 +14476,11 @@
         <v>14</v>
       </c>
       <c r="D326" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E326"/>
       <c r="F326" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G326" t="s">
         <v>19</v>
@@ -14505,13 +14506,13 @@
         <v>14</v>
       </c>
       <c r="D327" t="s">
+        <v>859</v>
+      </c>
+      <c r="E327" t="s">
         <v>860</v>
       </c>
-      <c r="E327" t="s">
+      <c r="F327" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="F327" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="G327" t="s">
         <v>19</v>
@@ -14537,13 +14538,13 @@
         <v>14</v>
       </c>
       <c r="D328" t="s">
+        <v>862</v>
+      </c>
+      <c r="E328" t="s">
         <v>863</v>
       </c>
-      <c r="E328" t="s">
+      <c r="F328" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="F328" s="1" t="s">
-        <v>865</v>
       </c>
       <c r="G328" t="s">
         <v>19</v>
@@ -14569,11 +14570,11 @@
         <v>14</v>
       </c>
       <c r="D329" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E329"/>
       <c r="F329" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G329" t="s">
         <v>19</v>
@@ -14599,13 +14600,13 @@
         <v>14</v>
       </c>
       <c r="D330" t="s">
+        <v>867</v>
+      </c>
+      <c r="E330" t="s">
         <v>868</v>
       </c>
-      <c r="E330" t="s">
+      <c r="F330" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="G330" t="s">
         <v>19</v>
@@ -14631,13 +14632,13 @@
         <v>14</v>
       </c>
       <c r="D331" t="s">
+        <v>870</v>
+      </c>
+      <c r="E331" t="s">
         <v>871</v>
       </c>
-      <c r="E331" t="s">
+      <c r="F331" s="1" t="s">
         <v>872</v>
-      </c>
-      <c r="F331" s="1" t="s">
-        <v>873</v>
       </c>
       <c r="G331" t="s">
         <v>19</v>
@@ -14663,13 +14664,13 @@
         <v>14</v>
       </c>
       <c r="D332" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E332" t="s">
+        <v>873</v>
+      </c>
+      <c r="F332" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="F332" s="1" t="s">
-        <v>875</v>
       </c>
       <c r="G332" t="s">
         <v>19</v>
@@ -14695,11 +14696,11 @@
         <v>14</v>
       </c>
       <c r="D333" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E333"/>
       <c r="F333" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G333" t="s">
         <v>19</v>
@@ -14725,13 +14726,13 @@
         <v>14</v>
       </c>
       <c r="D334" t="s">
+        <v>877</v>
+      </c>
+      <c r="E334" t="s">
         <v>878</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="F334" s="1" t="s">
-        <v>880</v>
       </c>
       <c r="G334" t="s">
         <v>19</v>
@@ -14757,13 +14758,13 @@
         <v>14</v>
       </c>
       <c r="D335" t="s">
+        <v>880</v>
+      </c>
+      <c r="E335" t="s">
         <v>881</v>
       </c>
-      <c r="E335" t="s">
+      <c r="F335" s="1" t="s">
         <v>882</v>
-      </c>
-      <c r="F335" s="1" t="s">
-        <v>883</v>
       </c>
       <c r="G335" t="s">
         <v>19</v>
@@ -14792,10 +14793,10 @@
         <v>120</v>
       </c>
       <c r="E336" t="s">
+        <v>883</v>
+      </c>
+      <c r="F336" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="F336" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="G336" t="s">
         <v>19</v>
@@ -14824,10 +14825,10 @@
         <v>120</v>
       </c>
       <c r="E337" t="s">
+        <v>885</v>
+      </c>
+      <c r="F337" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="F337" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="G337" t="s">
         <v>19</v>
@@ -14856,10 +14857,10 @@
         <v>120</v>
       </c>
       <c r="E338" t="s">
+        <v>887</v>
+      </c>
+      <c r="F338" s="1" t="s">
         <v>888</v>
-      </c>
-      <c r="F338" s="1" t="s">
-        <v>889</v>
       </c>
       <c r="G338" t="s">
         <v>19</v>
@@ -14888,10 +14889,10 @@
         <v>120</v>
       </c>
       <c r="E339" t="s">
+        <v>889</v>
+      </c>
+      <c r="F339" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="F339" s="1" t="s">
-        <v>891</v>
       </c>
       <c r="G339" t="s">
         <v>19</v>
@@ -14920,10 +14921,10 @@
         <v>87</v>
       </c>
       <c r="E340" t="s">
+        <v>891</v>
+      </c>
+      <c r="F340" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="F340" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="G340" t="s">
         <v>19</v>
@@ -14952,10 +14953,10 @@
         <v>579</v>
       </c>
       <c r="E341" t="s">
+        <v>893</v>
+      </c>
+      <c r="F341" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="F341" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="G341" t="s">
         <v>19</v>
@@ -14984,10 +14985,10 @@
         <v>96</v>
       </c>
       <c r="E342" t="s">
+        <v>895</v>
+      </c>
+      <c r="F342" t="s">
         <v>896</v>
-      </c>
-      <c r="F342" t="s">
-        <v>897</v>
       </c>
       <c r="G342" t="s">
         <v>19</v>

--- a/collected-data.xlsx
+++ b/collected-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-26.04\home\leo\OS-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E655A06D-A549-4DEB-B9BA-86884517BADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3DEBE6-1FAB-4239-A531-EFBCFC862506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
